--- a/Confluence/confluence_2/star_fact_issuer_exposure.xlsx
+++ b/Confluence/confluence_2/star_fact_issuer_exposure.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -166,8 +166,86 @@
       <color rgb="001A5C38"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="007F8C84"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A2B22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A2B22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="003D5247"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A5C38"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="003D5247"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E8B57"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A2B22"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A2B22"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="003D5247"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00A8362A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +276,28 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A5C38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF7F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFCFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -221,11 +319,70 @@
         <color rgb="00B8B0A0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8B0A0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8B0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8B0A0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8B0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8B0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8B0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8B0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8B0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E0DDD5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E0DDD5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0DDD5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0DDD5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -326,6 +483,60 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -400,6 +611,226 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Risk Data Platform</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>Three-part name in the form catalog.schema.table. Must already exist in Unity Catalog or be the table you are about to create. Example: creditrisk.xvala_xva.star_fact_issuer_exposure.</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>A clear description that names the grain (what one row represents) and the business meaning. Becomes the table COMMENT in Unity Catalog. Example: 'Daily snapshot of indirect issuer exposure. One row per agreement per counterparty per as-of date per issuer.' Avoid jargon — consumers across Risk read this.</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>The malcode of the application that produces and owns this dataset. Must match an entry in the app registry.</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>The Risk product group this table belongs to. Used to route the table to the right product-group owner during Phase 2 conformity.</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>The engineering team accountable for the producing application. Free text. Use the team name as it appears in your service catalog.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>How rows arrive in this table. cdc = change-data-capture incremental updates. full_load = entire table replaced each run. streaming = continuous append. file_drop = batch file ingestion. api = pulled from an upstream API.</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>The engineering team accountable for the physical table — who to contact if it breaks. Often the same as Source team owner; can differ for shared infrastructure tables. Free text.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Sensitivity classification per TD policy. public = no restriction. internal = TD employees only. confidential = need-to-know. restricted = formal access approval required. mnpi = material non-public information, special handling required.</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>Set to 'true' if any column in this table contains personally identifiable information. Default-absent: leave blank if no PII. When set, individual PII columns must also be marked PII=yes on the Columns sheet.</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>Where this table sits in its lifecycle. draft = being developed, not yet for consumption. active = in production use. deprecated = still available but consumers should migrate off. retired = read-only historical access. sunset = scheduled for removal by a specific date.</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>Determines whether this table appears in the Risk Data Catalog and is discoverable by consumers outside the producing team. yes = visible. no = internal staging or intermediate table, hidden from consumer catalog. This field MUST always be set explicitly — no default.</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>Structural type. dim = dimension table (one row per entity). fact = fact table (measures, one row per event or snapshot). obt = one big table (denormalised). lookup = small reference table. view = SQL view. materialized_view = pre-computed view. table = generic Delta table.</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>How often new data lands in this table.</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>The committed time by which a refresh must be complete, in plain language. Example: 'daily_by_07:00_EST' or 'monthly_by_business_day_3'. Free text — use a consistent convention across your app.</t>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>Set to 'true' if monetary amounts in this table have been converted from native currency to a reporting currency. Default-absent: leave blank if amounts are in native currency. When 'true', set Reporting currency, FX source, and FX rate date.</t>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0">
+      <text>
+        <t>If FX applied = true, the currency that monetary amounts have been converted to. If FX applied is blank, leave this blank (amounts are in native currency).</t>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0">
+      <text>
+        <t>Source of the FX rates used for conversion. Leave blank to inherit the schema-level default. Set only when this specific table uses a different FX source than the rest of the schema.</t>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
+      <text>
+        <t>Which date's FX rates were used to convert amounts. business_date = the as-of date of the row. business_date-1 = the prior business day's rate. month_end = end of month rate.</t>
+      </text>
+    </comment>
+    <comment ref="A23" authorId="0" shapeId="0">
+      <text>
+        <t>Set to 'true' if the table preserves the original native-currency columns alongside the FX-converted reporting-currency columns. Default-absent: leave blank if only converted amounts are present. Allows downstream consumers to access original values.</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="0" shapeId="0">
+      <text>
+        <t>Free-text override of the schema-level precedence rule for this table only. Use only when this table needs different source-precedence than the schema default. Format: '&lt;attribute&gt;:&lt;source1&gt;&gt;&lt;source2&gt;'. Example: 'issuer_rating:sp&gt;moodys'. Leave blank to inherit the schema default.</t>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0">
+      <text>
+        <t>Free-text notes for the data team. NOT published in the Risk Data Catalog. NOT visible to consumers. Use for known caveats, late-arriving data patterns, contact info for tricky edge cases, etc.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Risk Data Platform</author>
+  </authors>
+  <commentList>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>The physical column name as it appears in the Delta table. Case-sensitive. Use snake_case by convention.</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Databricks SQL data type. For DECIMAL, specify precision and scale: DECIMAL(18,2). For ARRAY, MAP, STRUCT, include the element type in the YAML definition; the dropdown lists the base type only.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>yes = NULL is allowed. no = NOT NULL will be enforced. Default to yes unless the column must have a value (e.g. primary key, required dimension).</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>One-sentence business meaning of the column. Becomes the column COMMENT in Unity Catalog — visible to all consumers. Be precise. Avoid app-internal jargon. Example: 'Internal counterparty identifier assigned by the credit team' — not 'cpty cd from upstream'.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable name for the column, as it should appear in business reports and the semantic layer. Example: physical column 'cpty_code' → alias 'Counterparty Code'. Used to bridge technical names with business language.</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Structural role of the column. key = primary or foreign key identifier. measure = numeric value being measured or calculated. dimension = categorical or descriptive attribute used for slicing. audit = system metadata (load_timestamp, etc.).</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>yes = this column is part of the primary key. For composite PKs, mark each PK column with yes. The set of PK columns expresses the table's grain — there is no separate grain field.</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>yes = this specific column contains personally identifiable information (name, email, SIN, account number, etc.). Triggers PII tagging in Unity Catalog. Must align with the table-level 'PII present' field.</t>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>Only fill in if the column has a fixed set of allowed values. Format: 'Sovereign,Bank,Corporate,Supranational,Agency'. Becomes a CHECK constraint in the DDL. Leave blank for free-form columns.</t>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="0" shapeId="0">
+      <text>
+        <t>If this column is a foreign key, specify the target column. Format: 'schema.table.column'. Example: 'creditrisk.xvala_xva.star_dim_counterparty.counterparty_code'. Leave blank for non-FK columns.</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>Only fill in for DATE or TIMESTAMP columns. The format consumers should expect. Leave blank for non-date columns.</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>Only fill in for TIMESTAMP columns. The timezone the value is recorded in. Leave blank for DATE and non-timestamp columns.</t>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0" shapeId="0">
+      <text>
+        <t>Only for Role=measure. additive = sums across all dimensions (e.g. trade count). semi-additive = sums across some but not all (e.g. balance sums across counterparties but not across dates). non-additive = does not sum (e.g. average, ratio).</t>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <t>Only for semi-additive measures. Comma-separated list of dimensions over which summing the measure is valid. Example for a balance: 'counterparty,agreement' (sums across counterparties and agreements, NOT across as_of_date).</t>
+      </text>
+    </comment>
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <t>Only for non-additive measures. Free-text warning that consumer tools should display when this measure is being aggregated. Example: 'Average — cannot be summed across rows.'</t>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
+      <text>
+        <t>Only for Role=measure. The unit the value is expressed in.</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <t>Only for Role=measure. The calculation methodology used to produce this value. Becomes a measure-level tag. Allows consumers to know which engine and version generated the number.</t>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. A URL or term ID that links this column to its definition in the Risk Data Catalog or business glossary. Helps consumers cross-reference the column to its canonical definition.</t>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <t>Free-text notes for the data team. NOT published in Unity Catalog. NOT visible to consumers. Use for caveats, known data-quality issues, edge cases, etc.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -691,13 +1122,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -730,6 +1161,9 @@
 Each workbook captures one table. Schema-level facts are repeated in each workbook for the same schema; consider that the schema sheet should match across workbooks for the same app.</t>
         </is>
       </c>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="35" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -744,6 +1178,9 @@
           <t>Open the 'Schema' sheet. Fill in the schema-level facts ONCE per schema. (Same across all table workbooks for the same app.)</t>
         </is>
       </c>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="35" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -751,6 +1188,9 @@
           <t>Open the 'Table properties' sheet. Fill in one value per row for this specific table.</t>
         </is>
       </c>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="35" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -758,6 +1198,9 @@
           <t>Open the 'Columns' sheet. Fill in one row per column.</t>
         </is>
       </c>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="35" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -765,6 +1208,9 @@
           <t>Open the 'Source catalog' sheet. Fill in one row per upstream feed this table consumes.</t>
         </is>
       </c>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="35" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -772,6 +1218,9 @@
           <t>Most boolean fields are default-absent — leave blank unless the answer is 'true' or 'yes'. The one exception: 'Visible to consumers' MUST always be set.</t>
         </is>
       </c>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -779,6 +1228,9 @@
           <t>When done, hand the workbook to the data team. They run the conversion to YAML and apply to UC.</t>
         </is>
       </c>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="35" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -798,6 +1250,8 @@
           <t>'Table description' and 'Column comment' become PUBLIC catalog descriptions consumers can see. 'Internal notes' is for the data team — not published, not consumer-facing.</t>
         </is>
       </c>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="35" t="n"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -810,6 +1264,8 @@
           <t>Boolean tags (PII present, FX applied, Known issue, Native columns kept) are OMITTED when false. Tag presence = the non-default state. ONE exception: 'Visible to consumers' must always be explicit.</t>
         </is>
       </c>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="35" t="n"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -822,6 +1278,8 @@
           <t>Some facts apply across an app (FX source, precedence, calendar) — set once on Schema sheet. If THIS table differs from the schema default, set the corresponding override at the table level. Otherwise leave blank to inherit.</t>
         </is>
       </c>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="35" t="n"/>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -834,6 +1292,8 @@
           <t>Mark Is primary key=yes on each PK column. Composite PK is supported (mark multiple columns). No separate grain marker — PK columns ARE the grain.</t>
         </is>
       </c>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="35" t="n"/>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -844,6 +1304,960 @@
       <c r="B20" s="7" t="inlineStr">
         <is>
           <t>x-measure.* fields apply only when Role=measure. Leave blank for non-measures.</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>4. Field reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>Every field in Table properties and Columns is described below. Hover over any field name in the sheets to see the same description as a cell comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>4a. Table properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>Allowed values</t>
+        </is>
+      </c>
+      <c r="D26" s="39" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>Table name</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>Three-part name in the form catalog.schema.table. Must already exist in Unity Catalog or be the table you are about to create. Example: creditrisk.xvala_xva.star_fact_issuer_exposure.</t>
+        </is>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>Table description</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>A clear description that names the grain (what one row represents) and the business meaning. Becomes the table COMMENT in Unity Catalog. Example: 'Daily snapshot of indirect issuer exposure. One row per agreement per counterparty per as-of date per issuer.' Avoid jargon — consumers across Risk read this.</t>
+        </is>
+      </c>
+      <c r="C28" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Producing app</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>The malcode of the application that produces and owns this dataset. Must match an entry in the app registry.</t>
+        </is>
+      </c>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>xvala,cmos,vs,rcs,alfa,crs,tams,lrm</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>Producer domain</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>The Risk product group this table belongs to. Used to route the table to the right product-group owner during Phase 2 conformity.</t>
+        </is>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>credit_risk,market_risk,funding,liquidity,shared</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>Source team owner</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>The engineering team accountable for the producing application. Free text. Use the team name as it appears in your service catalog.</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Load pattern</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>How rows arrive in this table. cdc = change-data-capture incremental updates. full_load = entire table replaced each run. streaming = continuous append. file_drop = batch file ingestion. api = pulled from an upstream API.</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>cdc,full_load,streaming,file_drop,api</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>Technical owner</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>The engineering team accountable for the physical table — who to contact if it breaks. Often the same as Source team owner; can differ for shared infrastructure tables. Free text.</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>Data classification</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>Sensitivity classification per TD policy. public = no restriction. internal = TD employees only. confidential = need-to-know. restricted = formal access approval required. mnpi = material non-public information, special handling required.</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>public,internal,confidential,restricted,mnpi</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>PII present (table)</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>Set to 'true' if any column in this table contains personally identifiable information. Default-absent: leave blank if no PII. When set, individual PII columns must also be marked PII=yes on the Columns sheet.</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>true (or blank)</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>Lifecycle status</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>Where this table sits in its lifecycle. draft = being developed, not yet for consumption. active = in production use. deprecated = still available but consumers should migrate off. retired = read-only historical access. sunset = scheduled for removal by a specific date.</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>draft,active,deprecated,retired,sunset</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>Visible to consumers</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Determines whether this table appears in the Risk Data Catalog and is discoverable by consumers outside the producing team. yes = visible. no = internal staging or intermediate table, hidden from consumer catalog. This field MUST always be set explicitly — no default.</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>yes,no</t>
+        </is>
+      </c>
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t>Table shape</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Structural type. dim = dimension table (one row per entity). fact = fact table (measures, one row per event or snapshot). obt = one big table (denormalised). lookup = small reference table. view = SQL view. materialized_view = pre-computed view. table = generic Delta table.</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>dim,fact,obt,lookup,view,materialized_view,table</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="40" t="inlineStr">
+        <is>
+          <t>Refresh frequency</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>How often new data lands in this table.</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>intraday,daily,weekly,monthly,quarterly,on_demand</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="40" t="inlineStr">
+        <is>
+          <t>Refresh SLA</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>The committed time by which a refresh must be complete, in plain language. Example: 'daily_by_07:00_EST' or 'monthly_by_business_day_3'. Free text — use a consistent convention across your app.</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t>FX applied</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>Set to 'true' if monetary amounts in this table have been converted from native currency to a reporting currency. Default-absent: leave blank if amounts are in native currency. When 'true', set Reporting currency, FX source, and FX rate date.</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>true (or blank)</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>Reporting currency</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>If FX applied = true, the currency that monetary amounts have been converted to. If FX applied is blank, leave this blank (amounts are in native currency).</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>USD,EUR,CAD,GBP</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="40" t="inlineStr">
+        <is>
+          <t>FX source (override)</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>Source of the FX rates used for conversion. Leave blank to inherit the schema-level default. Set only when this specific table uses a different FX source than the rest of the schema.</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>MIDAS,LAMP,Bloomberg</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>FX rate date</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>Which date's FX rates were used to convert amounts. business_date = the as-of date of the row. business_date-1 = the prior business day's rate. month_end = end of month rate.</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>business_date,business_date-1,month_end</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t>Native columns kept</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>Set to 'true' if the table preserves the original native-currency columns alongside the FX-converted reporting-currency columns. Default-absent: leave blank if only converted amounts are present. Allows downstream consumers to access original values.</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>true (or blank)</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t>Precedence override</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Free-text override of the schema-level precedence rule for this table only. Use only when this table needs different source-precedence than the schema default. Format: '&lt;attribute&gt;:&lt;source1&gt;&gt;&lt;source2&gt;'. Example: 'issuer_rating:sp&gt;moodys'. Leave blank to inherit the schema default.</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t>Internal notes</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>Free-text notes for the data team. NOT published in the Risk Data Catalog. NOT visible to consumers. Use for known caveats, late-arriving data patterns, contact info for tricky edge cases, etc.</t>
+        </is>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="38" t="inlineStr">
+        <is>
+          <t>4b. Columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>Allowed values</t>
+        </is>
+      </c>
+      <c r="D50" s="39" t="inlineStr">
+        <is>
+          <t>When to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="40" t="inlineStr">
+        <is>
+          <t>Column name</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>The physical column name as it appears in the Delta table. Case-sensitive. Use snake_case by convention.</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D51" s="45" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
+        <is>
+          <t>Databricks SQL data type. For DECIMAL, specify precision and scale: DECIMAL(18,2). For ARRAY, MAP, STRUCT, include the element type in the YAML definition; the dropdown lists the base type only.</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>STRING,INT,BIGINT,SMALLINT,TINYINT,FLOAT,DOUBLE,DECIMAL,DATE,TIMESTAMP,BOOLEAN,BINARY,ARRAY,MAP,STRUCT,VARIANT</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="40" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="inlineStr">
+        <is>
+          <t>yes = NULL is allowed. no = NOT NULL will be enforced. Default to yes unless the column must have a value (e.g. primary key, required dimension).</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>yes,no</t>
+        </is>
+      </c>
+      <c r="D53" s="45" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t>Column comment</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
+          <t>One-sentence business meaning of the column. Becomes the column COMMENT in Unity Catalog — visible to all consumers. Be precise. Avoid app-internal jargon. Example: 'Internal counterparty identifier assigned by the credit team' — not 'cpty cd from upstream'.</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D54" s="45" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="40" t="inlineStr">
+        <is>
+          <t>Alias (business name)</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
+          <t>Human-readable name for the column, as it should appear in business reports and the semantic layer. Example: physical column 'cpty_code' → alias 'Counterparty Code'. Used to bridge technical names with business language.</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr">
+        <is>
+          <t>every column (use physical name if no business alias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>Structural role of the column. key = primary or foreign key identifier. measure = numeric value being measured or calculated. dimension = categorical or descriptive attribute used for slicing. audit = system metadata (load_timestamp, etc.).</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>key,measure,dimension,audit</t>
+        </is>
+      </c>
+      <c r="D56" s="45" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="40" t="inlineStr">
+        <is>
+          <t>Is primary key</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>yes = this column is part of the primary key. For composite PKs, mark each PK column with yes. The set of PK columns expresses the table's grain — there is no separate grain field.</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>yes,no</t>
+        </is>
+      </c>
+      <c r="D57" s="45" t="inlineStr">
+        <is>
+          <t>PK columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="40" t="inlineStr">
+        <is>
+          <t>PII (column)</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>yes = this specific column contains personally identifiable information (name, email, SIN, account number, etc.). Triggers PII tagging in Unity Catalog. Must align with the table-level 'PII present' field.</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>yes,no</t>
+        </is>
+      </c>
+      <c r="D58" s="45" t="inlineStr">
+        <is>
+          <t>PII columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="40" t="inlineStr">
+        <is>
+          <t>Allowed values</t>
+        </is>
+      </c>
+      <c r="B59" s="41" t="inlineStr">
+        <is>
+          <t>Only fill in if the column has a fixed set of allowed values. Format: 'Sovereign,Bank,Corporate,Supranational,Agency'. Becomes a CHECK constraint in the DDL. Leave blank for free-form columns.</t>
+        </is>
+      </c>
+      <c r="C59" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D59" s="45" t="inlineStr">
+        <is>
+          <t>enum columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="40" t="inlineStr">
+        <is>
+          <t>FK references</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>If this column is a foreign key, specify the target column. Format: 'schema.table.column'. Example: 'creditrisk.xvala_xva.star_dim_counterparty.counterparty_code'. Leave blank for non-FK columns.</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D60" s="45" t="inlineStr">
+        <is>
+          <t>foreign key columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="B61" s="41" t="inlineStr">
+        <is>
+          <t>Only fill in for DATE or TIMESTAMP columns. The format consumers should expect. Leave blank for non-date columns.</t>
+        </is>
+      </c>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD,YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>DATE and TIMESTAMP columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="40" t="inlineStr">
+        <is>
+          <t>Timezone</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>Only fill in for TIMESTAMP columns. The timezone the value is recorded in. Leave blank for DATE and non-timestamp columns.</t>
+        </is>
+      </c>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>EST,UTC,America/New_York</t>
+        </is>
+      </c>
+      <c r="D62" s="45" t="inlineStr">
+        <is>
+          <t>TIMESTAMP columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="40" t="inlineStr">
+        <is>
+          <t>Measure — aggregation</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
+          <t>Only for Role=measure. additive = sums across all dimensions (e.g. trade count). semi-additive = sums across some but not all (e.g. balance sums across counterparties but not across dates). non-additive = does not sum (e.g. average, ratio).</t>
+        </is>
+      </c>
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>additive,semi-additive,non-additive</t>
+        </is>
+      </c>
+      <c r="D63" s="45" t="inlineStr">
+        <is>
+          <t>measure columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="40" t="inlineStr">
+        <is>
+          <t>Measure — safe dims</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
+        <is>
+          <t>Only for semi-additive measures. Comma-separated list of dimensions over which summing the measure is valid. Example for a balance: 'counterparty,agreement' (sums across counterparties and agreements, NOT across as_of_date).</t>
+        </is>
+      </c>
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D64" s="45" t="inlineStr">
+        <is>
+          <t>measure columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="40" t="inlineStr">
+        <is>
+          <t>Measure — warning</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
+          <t>Only for non-additive measures. Free-text warning that consumer tools should display when this measure is being aggregated. Example: 'Average — cannot be summed across rows.'</t>
+        </is>
+      </c>
+      <c r="C65" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D65" s="45" t="inlineStr">
+        <is>
+          <t>measure columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="40" t="inlineStr">
+        <is>
+          <t>Measure — unit</t>
+        </is>
+      </c>
+      <c r="B66" s="41" t="inlineStr">
+        <is>
+          <t>Only for Role=measure. The unit the value is expressed in.</t>
+        </is>
+      </c>
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>USD,EUR,percent,count,bps,ratio,days</t>
+        </is>
+      </c>
+      <c r="D66" s="45" t="inlineStr">
+        <is>
+          <t>measure columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="40" t="inlineStr">
+        <is>
+          <t>Measure — methodology</t>
+        </is>
+      </c>
+      <c r="B67" s="41" t="inlineStr">
+        <is>
+          <t>Only for Role=measure. The calculation methodology used to produce this value. Becomes a measure-level tag. Allows consumers to know which engine and version generated the number.</t>
+        </is>
+      </c>
+      <c r="C67" s="42" t="inlineStr">
+        <is>
+          <t>CCR_ENGINE_v4.2,SA-CCR,CEM,internal_model,vendor_xva</t>
+        </is>
+      </c>
+      <c r="D67" s="45" t="inlineStr">
+        <is>
+          <t>measure columns only</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="40" t="inlineStr">
+        <is>
+          <t>Glossary term link</t>
+        </is>
+      </c>
+      <c r="B68" s="41" t="inlineStr">
+        <is>
+          <t>Optional. A URL or term ID that links this column to its definition in the Risk Data Catalog or business glossary. Helps consumers cross-reference the column to its canonical definition.</t>
+        </is>
+      </c>
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D68" s="45" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="40" t="inlineStr">
+        <is>
+          <t>Internal notes</t>
+        </is>
+      </c>
+      <c r="B69" s="41" t="inlineStr">
+        <is>
+          <t>Free-text notes for the data team. NOT published in Unity Catalog. NOT visible to consumers. Use for caveats, known data-quality issues, edge cases, etc.</t>
+        </is>
+      </c>
+      <c r="C69" s="42" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="D69" s="45" t="inlineStr">
+        <is>
+          <t>optional</t>
         </is>
       </c>
     </row>
@@ -856,11 +2270,11 @@
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
@@ -2782,6 +4196,12 @@
           <t>ODCS reference: paths follow Open Data Contract Standard v3. Fields with paths starting 'customProperties.' are TD extensions outside the ODCS core schema (carried in the customProperties block). Fields starting with 'schema[]', 'team[]', 'slaProperties[]', 'domain', 'status' use ODCS-native attributes.</t>
         </is>
       </c>
+      <c r="B60" s="34" t="n"/>
+      <c r="C60" s="34" t="n"/>
+      <c r="D60" s="34" t="n"/>
+      <c r="E60" s="34" t="n"/>
+      <c r="F60" s="34" t="n"/>
+      <c r="G60" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2944,12 +4364,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -2960,413 +4380,413 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>One value per row. Worked example shown — replace values for your table.</t>
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>Fill one value per row for this table. Hover over a field name to see the full description.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Allowed values / examples</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="D4" s="48" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Table name</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Fully qualified Unity Catalog name.</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="D5" s="48" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Table description</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer.</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>Example: 'Daily snapshot of indirect issuer exposure. One row per agreement per counterparty per as-of date per issuer.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>One-sentence description with grain. Public-facing — consumers will see this.</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Producing app</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>xvala</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>xvala · cmos · vs · rcs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>The app that produces this table. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>Producer domain</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>credit_risk</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>credit_risk · market_risk · funding · liquidity · shared</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>Business domain this table belongs to. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Source team owner</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>ccr_engine_team</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>Team that owns the producing app.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>Team responsible for the producing app.</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>Load pattern</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>file_drop</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>cdc · full_load · streaming · file_drop · api</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>How data lands in the table. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>Technical owner</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>ccr_engine_team</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>Technical team accountable for the table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>Technical contact for this specific table.</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>Data classification</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>confidential</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>public · internal · confidential · restricted · mnpi</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>Sensitivity level. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>PII present (table)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>true · blank (default-absent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="B13" s="50" t="n"/>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>true if any column contains PII; blank otherwise. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>Lifecycle status</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>draft · active · deprecated · retired · sunset</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>Current state of the table. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D14" s="48" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Visible to consumers</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>yes · no (REQUIRED on every table)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>REQUIRED. yes = exposed to consumers. no = internal only. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>Table shape</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="50" t="inlineStr">
         <is>
           <t>fact</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>dim · fact · obt · lookup · view · materialized_view · table</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>Structural pattern of the table. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D16" s="48" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>Refresh frequency</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>intraday · daily · weekly · monthly · quarterly · on_demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>How often the table refreshes. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>Refresh SLA</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="50" t="inlineStr">
         <is>
           <t>daily_by_07:00_EST</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>daily_by_07:00_EST</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>Time by which refresh must complete on a refresh day.</t>
+        </is>
+      </c>
+      <c r="D18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>FX applied</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="50" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>true · blank (default-absent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>true if monetary amounts are FX-converted; blank otherwise. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Reporting currency</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>USD · EUR · CAD · GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>Currency monetary amounts are in. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>FX source (override)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>MIDAS · LAMP · Bloomberg · blank (inherit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>FX rate source — overrides schema default. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>FX rate date</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="50" t="inlineStr">
         <is>
           <t>business_date</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>business_date · business_date-1 · month_end</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>Which date's FX rates were used. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D22" s="48" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>Native columns kept</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr"/>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>true · blank (default-absent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="B23" s="50" t="n"/>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>true if native-currency columns are preserved alongside converted ones. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="49" t="inlineStr">
         <is>
           <t>Precedence override</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>issuer_rating:sp · blank (inherit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>Known issue present</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>true · blank (default-absent)</t>
-        </is>
-      </c>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>Optional. Override the schema-level precedence rule for this table.</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>Internal notes</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="inlineStr">
+        <is>
+          <t>Late-arriving issuer ratings backfilled within 2 days of as_of_date.</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="inlineStr">
+        <is>
+          <t>Not published. For the data team's reference.</t>
+        </is>
+      </c>
+      <c r="D25" s="48" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>Known issue tracker</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>JIRA-CCR-1847</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>JIRA-CCR-1847</t>
-        </is>
-      </c>
+      <c r="A26" s="54" t="n"/>
+      <c r="B26" s="54" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="48" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Internal notes</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Late-arriving issuer ratings backfilled within 2 days of as_of_date.</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>Example: 'Late-arriving issuer ratings backfilled within 2 days.'</t>
-        </is>
-      </c>
+      <c r="A27" s="54" t="n"/>
+      <c r="B27" s="54" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="14">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"xvala,cmos,vs,rcs"</formula1>
+      <formula1>"xvala,cmos,vs,rcs,alfa,crs,tams,lrm"</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"credit_risk,market_risk,funding,liquidity,shared"</formula1>
@@ -3376,6 +4796,9 @@
     </dataValidation>
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"public,internal,confidential,restricted,mnpi"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true"</formula1>
     </dataValidation>
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"draft,active,deprecated,retired,sunset"</formula1>
@@ -3389,6 +4812,9 @@
     <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"intraday,daily,weekly,monthly,quarterly,on_demand"</formula1>
     </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true"</formula1>
+    </dataValidation>
     <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"USD,EUR,CAD,GBP"</formula1>
     </dataValidation>
@@ -3398,9 +4824,13 @@
     <dataValidation sqref="B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"business_date,business_date-1,month_end"</formula1>
     </dataValidation>
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3413,197 +4843,245 @@
   <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Columns — star_fact_issuer_exposure</t>
+      <c r="A1" s="55" t="inlineStr">
+        <is>
+          <t>Columns — one row per column</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>One row per column. Worked example shown.</t>
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>Fill one row per column in your table. Hover over a header to see the full field description.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>Column name</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Column comment</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Alias (business name)</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>Is primary key</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="56" t="inlineStr">
         <is>
           <t>PII (column)</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="J4" s="56" t="inlineStr">
         <is>
           <t>FK references</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="K4" s="56" t="inlineStr">
         <is>
           <t>Date format</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="L4" s="56" t="inlineStr">
         <is>
           <t>Timezone</t>
         </is>
       </c>
-      <c r="M4" s="22" t="inlineStr">
+      <c r="M4" s="56" t="inlineStr">
         <is>
           <t>Measure — aggregation</t>
         </is>
       </c>
-      <c r="N4" s="22" t="inlineStr">
+      <c r="N4" s="56" t="inlineStr">
         <is>
           <t>Measure — safe dims</t>
         </is>
       </c>
-      <c r="O4" s="22" t="inlineStr">
+      <c r="O4" s="56" t="inlineStr">
         <is>
           <t>Measure — warning</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr">
+      <c r="P4" s="56" t="inlineStr">
         <is>
           <t>Measure — unit</t>
         </is>
       </c>
-      <c r="Q4" s="22" t="inlineStr">
+      <c r="Q4" s="56" t="inlineStr">
         <is>
           <t>Measure — methodology</t>
         </is>
       </c>
-      <c r="R4" s="22" t="inlineStr">
+      <c r="R4" s="56" t="inlineStr">
         <is>
           <t>Glossary term link</t>
         </is>
       </c>
-      <c r="S4" s="22" t="inlineStr">
+      <c r="S4" s="56" t="inlineStr">
         <is>
           <t>Internal notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>issuer_exposure_key</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>Synthetic unique identifier for each issuer exposure row.</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t>Issuer Exposure Key</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="G5" s="24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H5" s="24" t="inlineStr"/>
-      <c r="I5" s="24" t="inlineStr"/>
-      <c r="J5" s="24" t="inlineStr"/>
-      <c r="K5" s="24" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr"/>
-      <c r="M5" s="24" t="inlineStr"/>
-      <c r="N5" s="24" t="inlineStr"/>
-      <c r="O5" s="24" t="inlineStr"/>
-      <c r="P5" s="24" t="inlineStr"/>
-      <c r="Q5" s="24" t="inlineStr"/>
-      <c r="R5" s="24" t="inlineStr"/>
-      <c r="S5" s="24" t="inlineStr"/>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Exact column name as in the table.</t>
+        </is>
+      </c>
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>Databricks SQL type. Dropdown.</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>yes if NULLs are allowed in this column. Dropdown.</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>Public business meaning. One sentence. Becomes column COMMENT in UC.</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>Human-readable name consumers see in reports.</t>
+        </is>
+      </c>
+      <c r="F5" s="57" t="inlineStr">
+        <is>
+          <t>What this column does in the table. Dropdown.</t>
+        </is>
+      </c>
+      <c r="G5" s="57" t="inlineStr">
+        <is>
+          <t>yes if this column is part of the table's primary key. Dropdown.</t>
+        </is>
+      </c>
+      <c r="H5" s="57" t="inlineStr">
+        <is>
+          <t>yes if this specific column contains PII. Dropdown.</t>
+        </is>
+      </c>
+      <c r="I5" s="57" t="inlineStr">
+        <is>
+          <t>For enumerations: comma-separated list. Becomes a CHECK constraint.</t>
+        </is>
+      </c>
+      <c r="J5" s="57" t="inlineStr">
+        <is>
+          <t>If foreign key, the target column. Format: schema.table.column</t>
+        </is>
+      </c>
+      <c r="K5" s="57" t="inlineStr">
+        <is>
+          <t>For DATE/TIMESTAMP only. The display format. Dropdown.</t>
+        </is>
+      </c>
+      <c r="L5" s="57" t="inlineStr">
+        <is>
+          <t>For TIMESTAMP only. The timezone the timestamp represents. Dropdown.</t>
+        </is>
+      </c>
+      <c r="M5" s="57" t="inlineStr">
+        <is>
+          <t>For measures only. How the measure behaves under aggregation. Dropdown.</t>
+        </is>
+      </c>
+      <c r="N5" s="57" t="inlineStr">
+        <is>
+          <t>For semi-additive measures: dimensions over which sum is valid. Comma-separated.</t>
+        </is>
+      </c>
+      <c r="O5" s="57" t="inlineStr">
+        <is>
+          <t>For non-additive measures: warning to display to consumers.</t>
+        </is>
+      </c>
+      <c r="P5" s="57" t="inlineStr">
+        <is>
+          <t>For measures only. Unit of the value. Dropdown.</t>
+        </is>
+      </c>
+      <c r="Q5" s="57" t="inlineStr">
+        <is>
+          <t>For measures only. Engine and version that produced this measure. Dropdown or free text.</t>
+        </is>
+      </c>
+      <c r="R5" s="57" t="inlineStr">
+        <is>
+          <t>Optional URL or term-ID linking to the Risk Data Catalog entry.</t>
+        </is>
+      </c>
+      <c r="S5" s="57" t="inlineStr">
+        <is>
+          <t>Not published. For the data team's reference.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>agreement_id</t>
+          <t>issuer_exposure_key</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>STRING</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -3613,17 +5091,17 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>Identifier of the collateral agreement under which exposure arose.</t>
+          <t>Synthetic unique identifier for each issuer exposure row.</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Agreement ID</t>
+          <t>Issuer Exposure Key</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>dimension</t>
+          <t>key</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
@@ -3655,7 +5133,7 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>counterparty_code</t>
+          <t>agreement_id</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
@@ -3670,12 +5148,12 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>Counterparty facing TD under this exposure.</t>
+          <t>Identifier of the collateral agreement under which exposure arose.</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Counterparty Code</t>
+          <t>Agreement ID</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -3692,7 +5170,7 @@
       <c r="I7" s="24" t="inlineStr"/>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code</t>
+          <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id</t>
         </is>
       </c>
       <c r="K7" s="24" t="inlineStr"/>
@@ -3704,7 +5182,7 @@
       <c r="Q7" s="24" t="inlineStr"/>
       <c r="R7" s="24" t="inlineStr">
         <is>
-          <t>counterparty</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="S7" s="24" t="inlineStr"/>
@@ -3712,12 +5190,12 @@
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>as_of_date</t>
+          <t>counterparty_code</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3727,12 +5205,12 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>Calculation snapshot date.</t>
+          <t>Counterparty facing TD under this exposure.</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>As Of Date</t>
+          <t>Counterparty Code</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -3747,7 +5225,11 @@
       </c>
       <c r="H8" s="24" t="inlineStr"/>
       <c r="I8" s="24" t="inlineStr"/>
-      <c r="J8" s="24" t="inlineStr"/>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code</t>
+        </is>
+      </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
@@ -3761,7 +5243,7 @@
       <c r="Q8" s="24" t="inlineStr"/>
       <c r="R8" s="24" t="inlineStr">
         <is>
-          <t>as_of_date</t>
+          <t>counterparty</t>
         </is>
       </c>
       <c r="S8" s="24" t="inlineStr"/>
@@ -3769,12 +5251,12 @@
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>issuer_name</t>
+          <t>as_of_date</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>STRING</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3784,12 +5266,12 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Name of the issuer of the collateral instrument.</t>
+          <t>Calculation snapshot date.</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>Issuer Name</t>
+          <t>As Of Date</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -3805,7 +5287,11 @@
       <c r="H9" s="24" t="inlineStr"/>
       <c r="I9" s="24" t="inlineStr"/>
       <c r="J9" s="24" t="inlineStr"/>
-      <c r="K9" s="24" t="inlineStr"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="L9" s="24" t="inlineStr"/>
       <c r="M9" s="24" t="inlineStr"/>
       <c r="N9" s="24" t="inlineStr"/>
@@ -3814,7 +5300,7 @@
       <c r="Q9" s="24" t="inlineStr"/>
       <c r="R9" s="24" t="inlineStr">
         <is>
-          <t>issuer</t>
+          <t>as_of_date</t>
         </is>
       </c>
       <c r="S9" s="24" t="inlineStr"/>
@@ -3822,7 +5308,7 @@
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>issuer_type</t>
+          <t>issuer_name</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -3837,12 +5323,12 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>Type of issuer.</t>
+          <t>Name of the issuer of the collateral instrument.</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>Issuer Type</t>
+          <t>Issuer Name</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -3852,7 +5338,7 @@
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr"/>
@@ -3871,7 +5357,7 @@
       <c r="Q10" s="24" t="inlineStr"/>
       <c r="R10" s="24" t="inlineStr">
         <is>
-          <t>issuer_type</t>
+          <t>issuer</t>
         </is>
       </c>
       <c r="S10" s="24" t="inlineStr"/>
@@ -3879,7 +5365,7 @@
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>issuer_rating</t>
+          <t>issuer_type</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
@@ -3889,17 +5375,17 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>External credit rating of the issuer at as_of_date.</t>
+          <t>Type of issuer.</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Issuer Rating</t>
+          <t>Issuer Type</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
@@ -3915,7 +5401,7 @@
       <c r="H11" s="24" t="inlineStr"/>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>AAA, AA+, AA, AA-, A+, A, A-, BBB+, BBB, BBB-, BB+, BB, BB-, NR</t>
+          <t>Sovereign, Bank, Corporate, Supranational, Agency</t>
         </is>
       </c>
       <c r="J11" s="24" t="inlineStr"/>
@@ -3928,7 +5414,7 @@
       <c r="Q11" s="24" t="inlineStr"/>
       <c r="R11" s="24" t="inlineStr">
         <is>
-          <t>credit_rating</t>
+          <t>issuer_type</t>
         </is>
       </c>
       <c r="S11" s="24" t="inlineStr"/>
@@ -3936,41 +5422,45 @@
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>collateral_value</t>
+          <t>issuer_rating</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2)</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>External credit rating of the issuer at as_of_date.</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>Issuer Rating</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>Market value of collateral posted, USD-equivalent at as_of_date FX.</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>Collateral Value</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>measure</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="H12" s="24" t="inlineStr"/>
-      <c r="I12" s="24" t="inlineStr"/>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>AAA, AA+, AA, AA-, A+, A, A-, BBB+, BBB, BBB-, BB+, BB, BB-, NR</t>
+        </is>
+      </c>
       <c r="J12" s="24" t="inlineStr"/>
       <c r="K12" s="24" t="inlineStr"/>
       <c r="L12" s="24" t="inlineStr"/>
@@ -4001,7 +5491,7 @@
       </c>
       <c r="R12" s="24" t="inlineStr">
         <is>
-          <t>collateral_value</t>
+          <t>credit_rating</t>
         </is>
       </c>
       <c r="S12" s="24" t="inlineStr"/>
@@ -4009,7 +5499,7 @@
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>indirect_exposure</t>
+          <t>collateral_value</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
@@ -4024,12 +5514,12 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>Indirect exposure to the issuer arising from the collateral, USD-equivalent.</t>
+          <t>Market value of collateral posted, USD-equivalent at as_of_date FX.</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>Indirect Exposure</t>
+          <t>Collateral Value</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -4074,7 +5564,7 @@
       </c>
       <c r="R13" s="24" t="inlineStr">
         <is>
-          <t>indirect_exposure</t>
+          <t>collateral_value</t>
         </is>
       </c>
       <c r="S13" s="24" t="inlineStr"/>
@@ -4082,12 +5572,12 @@
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>load_timestamp</t>
+          <t>indirect_exposure</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DECIMAL(18,2)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -4097,17 +5587,17 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>When this row was loaded.</t>
+          <t>Indirect exposure to the issuer arising from the collateral, USD-equivalent.</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Load Timestamp</t>
+          <t>Indirect Exposure</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
@@ -4128,27 +5618,87 @@
           <t>UTC</t>
         </is>
       </c>
-      <c r="M14" s="24" t="inlineStr"/>
-      <c r="N14" s="24" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr"/>
-      <c r="P14" s="24" t="inlineStr"/>
-      <c r="Q14" s="24" t="inlineStr"/>
-      <c r="R14" s="24" t="inlineStr"/>
+      <c r="M14" s="24" t="inlineStr">
+        <is>
+          <t>semi-additive</t>
+        </is>
+      </c>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
+          <t>counterparty, agreement, issuer</t>
+        </is>
+      </c>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>Do not sum across as_of_date — use latest snapshot value.</t>
+        </is>
+      </c>
+      <c r="P14" s="24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q14" s="24" t="inlineStr">
+        <is>
+          <t>CCR_ENGINE_v4.2</t>
+        </is>
+      </c>
+      <c r="R14" s="24" t="inlineStr">
+        <is>
+          <t>indirect_exposure</t>
+        </is>
+      </c>
       <c r="S14" s="24" t="inlineStr"/>
     </row>
     <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="25" t="inlineStr"/>
-      <c r="B15" s="25" t="inlineStr"/>
-      <c r="C15" s="25" t="inlineStr"/>
-      <c r="D15" s="25" t="inlineStr"/>
-      <c r="E15" s="25" t="inlineStr"/>
-      <c r="F15" s="25" t="inlineStr"/>
-      <c r="G15" s="25" t="inlineStr"/>
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>load_timestamp</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>When this row was loaded.</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Load Timestamp</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="H15" s="25" t="inlineStr"/>
       <c r="I15" s="25" t="inlineStr"/>
       <c r="J15" s="25" t="inlineStr"/>
-      <c r="K15" s="25" t="inlineStr"/>
-      <c r="L15" s="25" t="inlineStr"/>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
       <c r="M15" s="25" t="inlineStr"/>
       <c r="N15" s="25" t="inlineStr"/>
       <c r="O15" s="25" t="inlineStr"/>
@@ -4587,40 +6137,44 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A16:S16"/>
+    <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <dataValidations count="9">
-    <dataValidation sqref="B5:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"STRING,DECIMAL"</formula1>
+  <dataValidations count="10">
+    <dataValidation sqref="B6:B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"STRING,INT,BIGINT,SMALLINT,TINYINT,FLOAT,DOUBLE,DECIMAL,DATE,TIMESTAMP,BOOLEAN,BINARY,ARRAY,MAP,STRUCT,VARIANT"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"key,measure,dimension,audit"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K6:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YYYY-MM-DD,YYYY-MM-DD HH:MM:SS"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EST,UTC,America/New_York"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M6:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"additive,semi-additive,non-additive"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"USD,EUR,percent,count,bps"</formula1>
+    <dataValidation sqref="P6:P45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"USD,EUR,percent,count,bps,ratio,days"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CCR_ENGINE_v4.2,SA-CCR,CEM"</formula1>
+    <dataValidation sqref="Q6:Q45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CCR_ENGINE_v4.2,SA-CCR,CEM,internal_model,vendor_xva"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/Confluence/confluence_2/star_fact_issuer_exposure.xlsx
+++ b/Confluence/confluence_2/star_fact_issuer_exposure.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="38">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -244,8 +244,24 @@
       <color rgb="00A8362A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001A5C38"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001A2B22"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -294,6 +310,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFCFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EFE1"/>
       </patternFill>
     </fill>
   </fills>
@@ -382,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -536,6 +557,16 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6821,7 +6852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A231"/>
+  <dimension ref="A1:A246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -6927,86 +6958,86 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="59" t="inlineStr">
+        <is>
+          <t># ═══ DESCRIPTION — purpose, scope, business meaning ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>description:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  purpose: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>team:</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - role: technicalOwner</t>
+          <t xml:space="preserve">  purpose: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    name: ccr_engine_team</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>slaProperties:</t>
+      <c r="A23" s="59" t="inlineStr">
+        <is>
+          <t># ═══ TEAM — ownership and contacts ═══</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: frequency</t>
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: daily</t>
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>team:</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: refreshSLA</t>
+          <t xml:space="preserve">  - role: technicalOwner</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: "daily_by_07:00_EST"</t>
+          <t xml:space="preserve">    name: ccr_engine_team</t>
         </is>
       </c>
     </row>
@@ -7018,177 +7049,177 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>schema:</t>
+      <c r="A29" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - name: star_fact_issuer_exposure</t>
+      <c r="A30" s="59" t="inlineStr">
+        <is>
+          <t># ═══ SLA — refresh cadence and timeliness commitments ═══</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    physicalName: d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+      <c r="A31" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    physicalType: fact</t>
+      <c r="A32" s="60" t="inlineStr">
+        <is>
+          <t>slaProperties:</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    description: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
+          <t xml:space="preserve">  - property: frequency</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">    value: daily</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    properties:</t>
+          <t xml:space="preserve">  - property: refreshSLA</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: issuer_exposure_key</t>
+          <t xml:space="preserve">    value: "daily_by_07:00_EST"</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: BIGINT</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Synthetic unique identifier for each issuer exposure row."</t>
+      <c r="A38" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Issuer Exposure Key"</t>
+      <c r="A39" s="59" t="inlineStr">
+        <is>
+          <t># ═══ SCHEMA — columns, types, constraints, measure metadata ═══</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        required: true</t>
+      <c r="A40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        primaryKey: true</t>
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>schema:</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve">  - name: star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">    physicalName: d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "key"</t>
+          <t xml:space="preserve">    physicalType: fact</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">    description: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: agreement_id</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
+          <t xml:space="preserve">    properties:</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Identifier of the collateral agreement under which exposure arose."</t>
+          <t xml:space="preserve">      - name: issuer_exposure_key</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Agreement ID"</t>
+          <t xml:space="preserve">        logicalType: BIGINT</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">        description: "Synthetic unique identifier for each issuer exposure row."</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        primaryKey: true</t>
+          <t xml:space="preserve">        businessName: "Issuer Exposure Key"</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        references:</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id"</t>
+          <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
@@ -7209,168 +7240,168 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "dimension"</t>
+          <t xml:space="preserve">            value: "key"</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "agreement"</t>
+          <t xml:space="preserve">      - name: agreement_id</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">        logicalType: STRING</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: counterparty_code</t>
+          <t xml:space="preserve">        description: "Identifier of the collateral agreement under which exposure arose."</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
+          <t xml:space="preserve">        businessName: "Agreement ID"</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Counterparty facing TD under this exposure."</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Counterparty Code"</t>
+          <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">        references:</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        primaryKey: true</t>
+          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id"</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        references:</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code"</t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve">            value: "dimension"</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "dimension"</t>
+          <t xml:space="preserve">            value: "agreement"</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "counterparty"</t>
+          <t xml:space="preserve">      - name: counterparty_code</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">        logicalType: STRING</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: as_of_date</t>
+          <t xml:space="preserve">        description: "Counterparty facing TD under this exposure."</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: DATE</t>
+          <t xml:space="preserve">        businessName: "Counterparty Code"</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Calculation snapshot date."</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "As Of Date"</t>
+          <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">        references:</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        primaryKey: true</t>
+          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code"</t>
         </is>
       </c>
     </row>
@@ -7398,98 +7429,98 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-date-format</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "YYYY-MM-DD"</t>
+          <t xml:space="preserve">            value: "counterparty"</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "as_of_date"</t>
+          <t xml:space="preserve">      - name: as_of_date</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">        logicalType: DATE</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: issuer_name</t>
+          <t xml:space="preserve">        description: "Calculation snapshot date."</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
+          <t xml:space="preserve">        businessName: "As Of Date"</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Name of the issuer of the collateral instrument."</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Issuer Name"</t>
+          <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        primaryKey: true</t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve">            value: "dimension"</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">          - property: x-date-format</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "dimension"</t>
+          <t xml:space="preserve">            value: "YYYY-MM-DD"</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7534,7 @@
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "issuer"</t>
+          <t xml:space="preserve">            value: "as_of_date"</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7548,7 @@
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: issuer_type</t>
+          <t xml:space="preserve">      - name: issuer_name</t>
         </is>
       </c>
     </row>
@@ -7531,14 +7562,14 @@
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Type of issuer."</t>
+          <t xml:space="preserve">        description: "Name of the issuer of the collateral instrument."</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Issuer Type"</t>
+          <t xml:space="preserve">        businessName: "Issuer Name"</t>
         </is>
       </c>
     </row>
@@ -7552,301 +7583,301 @@
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        validValues:</t>
+          <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "Sovereign"</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "Bank"</t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "Corporate"</t>
+          <t xml:space="preserve">            value: "dimension"</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "Supranational"</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "Agency"</t>
+          <t xml:space="preserve">            value: "issuer"</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">      - name: issuer_type</t>
         </is>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "dimension"</t>
+          <t xml:space="preserve">        logicalType: STRING</t>
         </is>
       </c>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve">        description: "Type of issuer."</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "issuer_type"</t>
+          <t xml:space="preserve">        businessName: "Issuer Type"</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: issuer_rating</t>
+          <t xml:space="preserve">        validValues:</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
+          <t xml:space="preserve">          - "Sovereign"</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "External credit rating of the issuer at as_of_date."</t>
+          <t xml:space="preserve">          - "Bank"</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Issuer Rating"</t>
+          <t xml:space="preserve">          - "Corporate"</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        validValues:</t>
+          <t xml:space="preserve">          - "Supranational"</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "AAA"</t>
+          <t xml:space="preserve">          - "Agency"</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "AA+"</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "AA"</t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "AA-"</t>
+          <t xml:space="preserve">            value: "dimension"</t>
         </is>
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "A+"</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "A"</t>
+          <t xml:space="preserve">            value: "issuer_type"</t>
         </is>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "A-"</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="129" ht="16" customHeight="1">
       <c r="A129" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "BBB+"</t>
+          <t xml:space="preserve">      - name: issuer_rating</t>
         </is>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
       <c r="A130" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "BBB"</t>
+          <t xml:space="preserve">        logicalType: STRING</t>
         </is>
       </c>
     </row>
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "BBB-"</t>
+          <t xml:space="preserve">        description: "External credit rating of the issuer at as_of_date."</t>
         </is>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "BB+"</t>
+          <t xml:space="preserve">        businessName: "Issuer Rating"</t>
         </is>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "BB"</t>
+          <t xml:space="preserve">        validValues:</t>
         </is>
       </c>
     </row>
     <row r="134" ht="16" customHeight="1">
       <c r="A134" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "BB-"</t>
+          <t xml:space="preserve">          - "AAA"</t>
         </is>
       </c>
     </row>
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - "NR"</t>
+          <t xml:space="preserve">          - "AA+"</t>
         </is>
       </c>
     </row>
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve">          - "AA"</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">          - "AA-"</t>
         </is>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "dimension"</t>
+          <t xml:space="preserve">          - "A+"</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve">          - "A"</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "credit_rating"</t>
+          <t xml:space="preserve">          - "A-"</t>
         </is>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">          - "BBB+"</t>
         </is>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: collateral_value</t>
+          <t xml:space="preserve">          - "BBB"</t>
         </is>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
+          <t xml:space="preserve">          - "BBB-"</t>
         </is>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1">
       <c r="A144" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Market value of collateral posted, USD-equivalent at as_of_date FX."</t>
+          <t xml:space="preserve">          - "BB+"</t>
         </is>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Collateral Value"</t>
+          <t xml:space="preserve">          - "BB"</t>
         </is>
       </c>
     </row>
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">          - "BB-"</t>
         </is>
       </c>
     </row>
     <row r="147" ht="16" customHeight="1">
       <c r="A147" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        unit: USD</t>
+          <t xml:space="preserve">          - "NR"</t>
         </is>
       </c>
     </row>
@@ -7867,572 +7898,657 @@
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "measure"</t>
+          <t xml:space="preserve">            value: "dimension"</t>
         </is>
       </c>
     </row>
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-aggregation</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "semi-additive"</t>
+          <t xml:space="preserve">            value: "credit_rating"</t>
         </is>
       </c>
     </row>
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-safe-dims</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "counterparty, agreement, issuer"</t>
+          <t xml:space="preserve">      - name: collateral_value</t>
         </is>
       </c>
     </row>
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-aggregation-warning</t>
+          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
         </is>
       </c>
     </row>
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "Do not sum across as_of_date — use latest snapshot value."</t>
+          <t xml:space="preserve">        description: "Market value of collateral posted, USD-equivalent at as_of_date FX."</t>
         </is>
       </c>
     </row>
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-methodology</t>
+          <t xml:space="preserve">        businessName: "Collateral Value"</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "CCR_ENGINE_v4.2"</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve">        unit: USD</t>
         </is>
       </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "collateral_value"</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: indirect_exposure</t>
+          <t xml:space="preserve">            value: "measure"</t>
         </is>
       </c>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
+          <t xml:space="preserve">          - property: x-aggregation</t>
         </is>
       </c>
     </row>
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "Indirect exposure to the issuer arising from the collateral, USD-equivalent."</t>
+          <t xml:space="preserve">            value: "semi-additive"</t>
         </is>
       </c>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Indirect Exposure"</t>
+          <t xml:space="preserve">          - property: x-safe-dims</t>
         </is>
       </c>
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">            value: "counterparty, agreement, issuer"</t>
         </is>
       </c>
     </row>
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        unit: USD</t>
+          <t xml:space="preserve">          - property: x-aggregation-warning</t>
         </is>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve">            value: "Do not sum across as_of_date — use latest snapshot value."</t>
         </is>
       </c>
     </row>
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">          - property: x-methodology</t>
         </is>
       </c>
     </row>
     <row r="170" ht="16" customHeight="1">
       <c r="A170" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "measure"</t>
+          <t xml:space="preserve">            value: "CCR_ENGINE_v4.2"</t>
         </is>
       </c>
     </row>
     <row r="171" ht="16" customHeight="1">
       <c r="A171" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-aggregation</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "semi-additive"</t>
+          <t xml:space="preserve">            value: "collateral_value"</t>
         </is>
       </c>
     </row>
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-safe-dims</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "counterparty, agreement, issuer"</t>
+          <t xml:space="preserve">      - name: indirect_exposure</t>
         </is>
       </c>
     </row>
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-aggregation-warning</t>
+          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
         </is>
       </c>
     </row>
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "Do not sum across as_of_date — use latest snapshot value."</t>
+          <t xml:space="preserve">        description: "Indirect exposure to the issuer arising from the collateral, USD-equivalent."</t>
         </is>
       </c>
     </row>
     <row r="177" ht="16" customHeight="1">
       <c r="A177" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-methodology</t>
+          <t xml:space="preserve">        businessName: "Indirect Exposure"</t>
         </is>
       </c>
     </row>
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "CCR_ENGINE_v4.2"</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+          <t xml:space="preserve">        unit: USD</t>
         </is>
       </c>
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "indirect_exposure"</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - name: load_timestamp</t>
+          <t xml:space="preserve">            value: "measure"</t>
         </is>
       </c>
     </row>
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        logicalType: TIMESTAMP</t>
+          <t xml:space="preserve">          - property: x-aggregation</t>
         </is>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        description: "When this row was loaded."</t>
+          <t xml:space="preserve">            value: "semi-additive"</t>
         </is>
       </c>
     </row>
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        businessName: "Load Timestamp"</t>
+          <t xml:space="preserve">          - property: x-safe-dims</t>
         </is>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        required: true</t>
+          <t xml:space="preserve">            value: "counterparty, agreement, issuer"</t>
         </is>
       </c>
     </row>
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">        customProperties:</t>
+          <t xml:space="preserve">          - property: x-aggregation-warning</t>
         </is>
       </c>
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+          <t xml:space="preserve">            value: "Do not sum across as_of_date — use latest snapshot value."</t>
         </is>
       </c>
     </row>
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "audit"</t>
+          <t xml:space="preserve">          - property: x-methodology</t>
         </is>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-date-format</t>
+          <t xml:space="preserve">            value: "CCR_ENGINE_v4.2"</t>
         </is>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "YYYY-MM-DD HH:MM:SS"</t>
+          <t xml:space="preserve">          - property: x-glossary-term</t>
         </is>
       </c>
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          - property: x-timezone</t>
+          <t xml:space="preserve">            value: "indirect_exposure"</t>
         </is>
       </c>
     </row>
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            value: "UTC"</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">      - name: load_timestamp</t>
         </is>
       </c>
     </row>
     <row r="195" ht="16" customHeight="1">
       <c r="A195" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">        logicalType: TIMESTAMP</t>
         </is>
       </c>
     </row>
     <row r="196" ht="16" customHeight="1">
-      <c r="A196" s="29" t="inlineStr">
-        <is>
-          <t># TD-specific extensions (x-* customProperties)</t>
+      <c r="A196" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "When this row was loaded."</t>
         </is>
       </c>
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="30" t="inlineStr">
         <is>
-          <t>customProperties:</t>
+          <t xml:space="preserve">        businessName: "Load Timestamp"</t>
         </is>
       </c>
     </row>
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-source-app</t>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: xvala</t>
+          <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
     <row r="200" ht="16" customHeight="1">
       <c r="A200" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-source-owner</t>
+          <t xml:space="preserve">          - property: x-column-role</t>
         </is>
       </c>
     </row>
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: ccr_engine_team</t>
+          <t xml:space="preserve">            value: "audit"</t>
         </is>
       </c>
     </row>
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-load-pattern</t>
+          <t xml:space="preserve">          - property: x-date-format</t>
         </is>
       </c>
     </row>
     <row r="203" ht="16" customHeight="1">
       <c r="A203" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: file_drop</t>
+          <t xml:space="preserve">            value: "YYYY-MM-DD HH:MM:SS"</t>
         </is>
       </c>
     </row>
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: dataClassification</t>
+          <t xml:space="preserve">          - property: x-timezone</t>
         </is>
       </c>
     </row>
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: confidential</t>
+          <t xml:space="preserve">            value: "UTC"</t>
         </is>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1">
       <c r="A206" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-visible</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="207" ht="16" customHeight="1">
       <c r="A207" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: yes</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- inherited from schema-level (set on ALTER SCHEMA) ----</t>
+      <c r="A208" s="29" t="inlineStr">
+        <is>
+          <t># TD-specific extensions (x-* customProperties)</t>
         </is>
       </c>
     </row>
     <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-source-catalog-url</t>
+      <c r="A209" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: "https://sharepoint.td.com/risk-data/xvala_source_catalog.xlsx"</t>
+      <c r="A210" s="59" t="inlineStr">
+        <is>
+          <t># ═══ CUSTOM PROPERTIES — TD-specific extensions (x-* tags) ═══</t>
         </is>
       </c>
     </row>
     <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-precedence-defaults</t>
+      <c r="A211" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="212" ht="16" customHeight="1">
-      <c r="A212" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: "issuer_rating:sp&gt;moodys&gt;internal"</t>
+      <c r="A212" s="60" t="inlineStr">
+        <is>
+          <t>customProperties:</t>
         </is>
       </c>
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-currency-fx-source-default</t>
+          <t xml:space="preserve">  - property: x-source-app</t>
         </is>
       </c>
     </row>
     <row r="214" ht="16" customHeight="1">
       <c r="A214" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: MIDAS</t>
+          <t xml:space="preserve">    value: xvala</t>
         </is>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-source-calendar</t>
+          <t xml:space="preserve">  - property: x-source-owner</t>
         </is>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1">
       <c r="A216" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: internal_business_calendar</t>
+          <t xml:space="preserve">    value: ccr_engine_team</t>
         </is>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- currency handling (this table) ----</t>
+      <c r="A217" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-load-pattern</t>
         </is>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1">
       <c r="A218" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-currency-applied</t>
+          <t xml:space="preserve">    value: file_drop</t>
         </is>
       </c>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: true</t>
+          <t xml:space="preserve">  - property: dataClassification</t>
         </is>
       </c>
     </row>
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-currency-reporting</t>
+          <t xml:space="preserve">    value: confidential</t>
         </is>
       </c>
     </row>
     <row r="221" ht="16" customHeight="1">
       <c r="A221" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: USD</t>
+          <t xml:space="preserve">  - property: x-visible</t>
         </is>
       </c>
     </row>
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-currency-fx-rate-date</t>
+          <t xml:space="preserve">    value: yes</t>
         </is>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1">
-      <c r="A223" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: business_date</t>
+      <c r="A223" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  # ---- inherited from schema-level (set on ALTER SCHEMA) ----</t>
         </is>
       </c>
     </row>
     <row r="224" ht="16" customHeight="1">
-      <c r="A224" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- known issues ----</t>
+      <c r="A224" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-source-catalog-url</t>
         </is>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1">
       <c r="A225" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-issue</t>
+          <t xml:space="preserve">    value: "https://sharepoint.td.com/risk-data/xvala_source_catalog.xlsx"</t>
         </is>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1">
       <c r="A226" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: true</t>
+          <t xml:space="preserve">  - property: x-precedence-defaults</t>
         </is>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1">
       <c r="A227" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-issue-tracker</t>
+          <t xml:space="preserve">    value: "issuer_rating:sp&gt;moodys&gt;internal"</t>
         </is>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1">
       <c r="A228" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    value: "JIRA-CCR-1847"</t>
+          <t xml:space="preserve">  - property: x-currency-fx-source-default</t>
         </is>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1">
-      <c r="A229" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- internal notes (not consumer-facing) ----</t>
+      <c r="A229" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: MIDAS</t>
         </is>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1">
       <c r="A230" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - property: x-internal-notes</t>
+          <t xml:space="preserve">  - property: x-source-calendar</t>
         </is>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1">
       <c r="A231" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: internal_business_calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  # ---- currency handling (this table) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-currency-applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-currency-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-currency-fx-rate-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: business_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="61" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="61" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="61" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="61" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="61" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  # ---- internal notes (not consumer-facing) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-internal-notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">    value: "Late-arriving issuer ratings backfilled within 2 days of as_of_date."</t>
         </is>

--- a/Confluence/confluence_2/star_fact_issuer_exposure.xlsx
+++ b/Confluence/confluence_2/star_fact_issuer_exposure.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -260,8 +260,17 @@
       <color rgb="001A2B22"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="002E8B57"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -315,6 +324,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EFE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A8362A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF8F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -403,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -568,6 +592,62 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -652,62 +732,62 @@
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
-        <t>Three-part name in the form catalog.schema.table. Must already exist in Unity Catalog or be the table you are about to create. Example: creditrisk.xvala_xva.star_fact_issuer_exposure.</t>
+        <t>Three-part name in the form catalog.schema.table. Example: creditrisk.xvala_xva.star_fact_issuer_exposure.</t>
       </text>
     </comment>
     <comment ref="A6" authorId="0" shapeId="0">
       <text>
-        <t>A clear description that names the grain (what one row represents) and the business meaning. Becomes the table COMMENT in Unity Catalog. Example: 'Daily snapshot of indirect issuer exposure. One row per agreement per counterparty per as-of date per issuer.' Avoid jargon — consumers across Risk read this.</t>
+        <t>A clear description that names the grain (what one row represents) and the business meaning. Becomes the table COMMENT in Unity Catalog.</t>
       </text>
     </comment>
     <comment ref="A7" authorId="0" shapeId="0">
       <text>
-        <t>The malcode of the application that produces and owns this dataset. Must match an entry in the app registry.</t>
+        <t>The malcode of the application that produces and owns this dataset.</t>
       </text>
     </comment>
     <comment ref="A8" authorId="0" shapeId="0">
       <text>
-        <t>The Risk product group this table belongs to. Used to route the table to the right product-group owner during Phase 2 conformity.</t>
+        <t>The Risk product group this table belongs to.</t>
       </text>
     </comment>
     <comment ref="A9" authorId="0" shapeId="0">
       <text>
-        <t>The engineering team accountable for the producing application. Free text. Use the team name as it appears in your service catalog.</t>
+        <t>The engineering team accountable for the producing application.</t>
       </text>
     </comment>
     <comment ref="A10" authorId="0" shapeId="0">
       <text>
-        <t>How rows arrive in this table. cdc = change-data-capture incremental updates. full_load = entire table replaced each run. streaming = continuous append. file_drop = batch file ingestion. api = pulled from an upstream API.</t>
+        <t>How rows arrive in this table. cdc = change-data-capture. full_load = entire table replaced. streaming = continuous append. file_drop = batch file. api = pulled from upstream API.</t>
       </text>
     </comment>
     <comment ref="A11" authorId="0" shapeId="0">
       <text>
-        <t>The engineering team accountable for the physical table — who to contact if it breaks. Often the same as Source team owner; can differ for shared infrastructure tables. Free text.</t>
+        <t>The engineering team accountable for the physical table.</t>
       </text>
     </comment>
     <comment ref="A12" authorId="0" shapeId="0">
       <text>
-        <t>Sensitivity classification per TD policy. public = no restriction. internal = TD employees only. confidential = need-to-know. restricted = formal access approval required. mnpi = material non-public information, special handling required.</t>
+        <t>Sensitivity classification per TD policy.</t>
       </text>
     </comment>
     <comment ref="A13" authorId="0" shapeId="0">
       <text>
-        <t>Set to 'true' if any column in this table contains personally identifiable information. Default-absent: leave blank if no PII. When set, individual PII columns must also be marked PII=yes on the Columns sheet.</t>
+        <t>Default-absent: leave blank if no PII.</t>
       </text>
     </comment>
     <comment ref="A14" authorId="0" shapeId="0">
       <text>
-        <t>Where this table sits in its lifecycle. draft = being developed, not yet for consumption. active = in production use. deprecated = still available but consumers should migrate off. retired = read-only historical access. sunset = scheduled for removal by a specific date.</t>
+        <t>Where this table sits in its lifecycle.</t>
       </text>
     </comment>
     <comment ref="A15" authorId="0" shapeId="0">
       <text>
-        <t>Determines whether this table appears in the Risk Data Catalog and is discoverable by consumers outside the producing team. yes = visible. no = internal staging or intermediate table, hidden from consumer catalog. This field MUST always be set explicitly — no default.</t>
+        <t>Determines whether this table appears in the Risk Data Catalog and is discoverable by consumers.</t>
       </text>
     </comment>
     <comment ref="A16" authorId="0" shapeId="0">
       <text>
-        <t>Structural type. dim = dimension table (one row per entity). fact = fact table (measures, one row per event or snapshot). obt = one big table (denormalised). lookup = small reference table. view = SQL view. materialized_view = pre-computed view. table = generic Delta table.</t>
+        <t>Structural type. dim/fact/obt/lookup/view/materialized_view/table.</t>
       </text>
     </comment>
     <comment ref="A17" authorId="0" shapeId="0">
@@ -717,42 +797,52 @@
     </comment>
     <comment ref="A18" authorId="0" shapeId="0">
       <text>
-        <t>The committed time by which a refresh must be complete, in plain language. Example: 'daily_by_07:00_EST' or 'monthly_by_business_day_3'. Free text — use a consistent convention across your app.</t>
+        <t>The committed time by which a refresh must be complete. Example: 'daily_by_07:00_EST'.</t>
       </text>
     </comment>
     <comment ref="A19" authorId="0" shapeId="0">
       <text>
-        <t>Set to 'true' if monetary amounts in this table have been converted from native currency to a reporting currency. Default-absent: leave blank if amounts are in native currency. When 'true', set Reporting currency, FX source, and FX rate date.</t>
+        <t>Default-absent: leave blank if amounts are in native currency.</t>
       </text>
     </comment>
     <comment ref="A20" authorId="0" shapeId="0">
       <text>
-        <t>If FX applied = true, the currency that monetary amounts have been converted to. If FX applied is blank, leave this blank (amounts are in native currency).</t>
+        <t>If FX applied = true, the currency that monetary amounts have been converted to.</t>
       </text>
     </comment>
     <comment ref="A21" authorId="0" shapeId="0">
       <text>
-        <t>Source of the FX rates used for conversion. Leave blank to inherit the schema-level default. Set only when this specific table uses a different FX source than the rest of the schema.</t>
+        <t>Leave blank to inherit the schema-level default.</t>
       </text>
     </comment>
     <comment ref="A22" authorId="0" shapeId="0">
       <text>
-        <t>Which date's FX rates were used to convert amounts. business_date = the as-of date of the row. business_date-1 = the prior business day's rate. month_end = end of month rate.</t>
+        <t>Which date's FX rates were used to convert amounts.</t>
       </text>
     </comment>
     <comment ref="A23" authorId="0" shapeId="0">
       <text>
-        <t>Set to 'true' if the table preserves the original native-currency columns alongside the FX-converted reporting-currency columns. Default-absent: leave blank if only converted amounts are present. Allows downstream consumers to access original values.</t>
+        <t>Default-absent: leave blank.</t>
       </text>
     </comment>
     <comment ref="A24" authorId="0" shapeId="0">
       <text>
-        <t>Free-text override of the schema-level precedence rule for this table only. Use only when this table needs different source-precedence than the schema default. Format: '&lt;attribute&gt;:&lt;source1&gt;&gt;&lt;source2&gt;'. Example: 'issuer_rating:sp&gt;moodys'. Leave blank to inherit the schema default.</t>
+        <t>Free-text override of the schema-level precedence rule for this table only.</t>
       </text>
     </comment>
     <comment ref="A25" authorId="0" shapeId="0">
       <text>
-        <t>Free-text notes for the data team. NOT published in the Risk Data Catalog. NOT visible to consumers. Use for known caveats, late-arriving data patterns, contact info for tricky edge cases, etc.</t>
+        <t>What this dataset affirmatively includes. Two facts with identical schema but different scopes are different facts — scope must be explicit. Example: 'Bilateral CSA agreements with eligible collateral. All counterparty regulatory regimes. End-of-day snapshots only.'</t>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0">
+      <text>
+        <t>What this dataset deliberately excludes. Surfaces invisible assumptions the producing app made. Example: 'Cleared trades. Exchange-traded positions. Tri-party agreements (handled by a separate fact). Trades in WIP or terminated status.'</t>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0">
+      <text>
+        <t>Free-text notes for the data team. NOT published in the Risk Data Catalog.</t>
       </text>
     </comment>
   </commentList>
@@ -767,97 +857,127 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>The physical column name as it appears in the Delta table. Case-sensitive. Use snake_case by convention.</t>
+        <t>The physical column name as it appears in the Delta table. Case-sensitive. snake_case by convention.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>Databricks SQL data type. For DECIMAL, specify precision and scale: DECIMAL(18,2). For ARRAY, MAP, STRUCT, include the element type in the YAML definition; the dropdown lists the base type only.</t>
+        <t>Databricks SQL data type. For DECIMAL, specify precision and scale: DECIMAL(18,2).</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>yes = NULL is allowed. no = NOT NULL will be enforced. Default to yes unless the column must have a value (e.g. primary key, required dimension).</t>
+        <t>yes = NULL is allowed. no = NOT NULL will be enforced.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>One-sentence business meaning of the column. Becomes the column COMMENT in Unity Catalog — visible to all consumers. Be precise. Avoid app-internal jargon. Example: 'Internal counterparty identifier assigned by the credit team' — not 'cpty cd from upstream'.</t>
+        <t>The base entity this column represents or derives from. Examples: 'Counterparty' for counterparty_code; 'Issuer' for issuer_type (a denormalised attribute of Issuer). Leave blank for fact-local columns (measures, audit fields, surrogate keys). The app's local name for the entity is fine — conformity work reconciles entity names across apps later.</t>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>Human-readable name for the column, as it should appear in business reports and the semantic layer. Example: physical column 'cpty_code' → alias 'Counterparty Code'. Used to bridge technical names with business language.</t>
+        <t>How this column relates to its base entity. Conventions: 'foreign key' for pure FK columns; 'denormalised attribute (&lt;attr&gt;)' for entity attributes materialised in the fact; 'trading counterparty', 'guarantor', 'reference obligor' etc. for disambiguating multi-role FKs; 'measure', 'audit', 'surrogate key' for fact-local columns.</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>Structural role of the column. key = primary or foreign key identifier. measure = numeric value being measured or calculated. dimension = categorical or descriptive attribute used for slicing. audit = system metadata (load_timestamp, etc.).</t>
+        <t>One-sentence business meaning. Becomes the column COMMENT in Unity Catalog. For columns with Base entity declared, this can be terse — the full definition lives in the entity's page. For fact-local columns (measures, audit), authoritative description needed here.</t>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>yes = this column is part of the primary key. For composite PKs, mark each PK column with yes. The set of PK columns expresses the table's grain — there is no separate grain field.</t>
+        <t>Human-readable name for the column. For Base-entity columns, often inherited from the entity's attribute name. For fact-local columns, authored here.</t>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>yes = this specific column contains personally identifiable information (name, email, SIN, account number, etc.). Triggers PII tagging in Unity Catalog. Must align with the table-level 'PII present' field.</t>
+        <t>Structural role. key = PK or FK identifier. measure = numeric value. dimension = categorical attribute. audit = system metadata. Different from 'Role' which captures semantic role relative to entity.</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>Only fill in if the column has a fixed set of allowed values. Format: 'Sovereign,Bank,Corporate,Supranational,Agency'. Becomes a CHECK constraint in the DDL. Leave blank for free-form columns.</t>
+        <t>yes = this column is part of the PK. For composite PKs, mark each PK column with yes.</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>If this column is a foreign key, specify the target column. Format: 'schema.table.column'. Example: 'creditrisk.xvala_xva.star_dim_counterparty.counterparty_code'. Leave blank for non-FK columns.</t>
+        <t>yes = this column contains personally identifiable information.</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>Only fill in for DATE or TIMESTAMP columns. The format consumers should expect. Leave blank for non-date columns.</t>
+        <t>Only fill in if the column has a fixed set of allowed values. For columns with Base entity, allowed values should ideally come from the entity's definition — duplicating here is OK but reconcile later. Becomes a CHECK constraint in the DDL.</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>Only fill in for TIMESTAMP columns. The timezone the value is recorded in. Leave blank for DATE and non-timestamp columns.</t>
+        <t>Target of the FK reference. Example: 'creditrisk.xvala_xva.star_dim_counterparty.counterparty_code'.</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>Only for Role=measure. additive = sums across all dimensions (e.g. trade count). semi-additive = sums across some but not all (e.g. balance sums across counterparties but not across dates). non-additive = does not sum (e.g. average, ratio).</t>
+        <t>Only fill in for DATE or TIMESTAMP columns.</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>Only for semi-additive measures. Comma-separated list of dimensions over which summing the measure is valid. Example for a balance: 'counterparty,agreement' (sums across counterparties and agreements, NOT across as_of_date).</t>
+        <t>Only fill in for TIMESTAMP columns.</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>Only for non-additive measures. Free-text warning that consumer tools should display when this measure is being aggregated. Example: 'Average — cannot be summed across rows.'</t>
+        <t>Only for Role(structural)=measure. additive/semi-additive/non-additive.</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>Only for Role=measure. The unit the value is expressed in.</t>
+        <t>Only for semi-additive measures.</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>Only for Role=measure. The calculation methodology used to produce this value. Becomes a measure-level tag. Allows consumers to know which engine and version generated the number.</t>
+        <t>Only for non-additive measures.</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>Optional. A URL or term ID that links this column to its definition in the Risk Data Catalog or business glossary. Helps consumers cross-reference the column to its canonical definition.</t>
+        <t>Only for measures. The unit the value is expressed in.</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>Free-text notes for the data team. NOT published in Unity Catalog. NOT visible to consumers. Use for caveats, known data-quality issues, edge cases, etc.</t>
+        <t>Only for measures. The calculation methodology used.</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. URL or term ID linking to the canonical definition.</t>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <t>Free-text notes for the data team. NOT published.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Risk Data Platform</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>For now, the Contract ID is the producing app's malcode (e.g., murex, goldensource, midas). This identifies the source app/system that owns the data. Versioning and richer Contract ID structure will come later.</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>Which Risk-declared entity does this source populate? Use entity names from Risk's conformed entity workbooks (Counterparty, Agreement, Issuer, etc.). The alignment carries forward to facts — facts reference these same entities via Base entity on each column. If the source provides reference data rather than entity rows (e.g., FX rates), note that explicitly.</t>
       </text>
     </comment>
   </commentList>
@@ -4399,8 +4519,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -4618,7 +4738,7 @@
           <t>Visible to consumers</t>
         </is>
       </c>
-      <c r="B15" s="53" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4752,7 +4872,7 @@
       </c>
       <c r="D22" s="48" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="49" t="inlineStr">
         <is>
           <t>Native columns kept</t>
@@ -4780,34 +4900,58 @@
       </c>
       <c r="D24" s="48" t="n"/>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="49" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>Includes</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="inlineStr">
+        <is>
+          <t>Bilateral CSA agreements with eligible collateral. All counterparty regulatory regimes. End-of-day snapshots only.</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="inlineStr">
+        <is>
+          <t>Affirmative scope. What's in this dataset.</t>
+        </is>
+      </c>
+      <c r="D25" s="48" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>Excludes</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>Cleared trades. Exchange-traded positions. Tri-party agreements (handled by separate fact). Trades in WIP or terminated status.</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>Out-of-scope. What's deliberately not in this dataset.</t>
+        </is>
+      </c>
+      <c r="D26" s="48" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>Internal notes</t>
         </is>
       </c>
-      <c r="B25" s="50" t="inlineStr">
+      <c r="B27" s="50" t="inlineStr">
         <is>
           <t>Late-arriving issuer ratings backfilled within 2 days of as_of_date.</t>
         </is>
       </c>
-      <c r="C25" s="51" t="inlineStr">
+      <c r="C27" s="51" t="inlineStr">
         <is>
           <t>Not published. For the data team's reference.</t>
         </is>
       </c>
-      <c r="D25" s="48" t="n"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="54" t="n"/>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="48" t="n"/>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="54" t="n"/>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
       <c r="D27" s="48" t="n"/>
     </row>
   </sheetData>
@@ -4871,28 +5015,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -4905,7 +5051,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="46" t="inlineStr">
         <is>
-          <t>Fill one row per column in your table. Hover over a header to see the full field description.</t>
+          <t>Fill one row per column. Hover over any header for the full description. Base entity + Role tell consumers where each column semantically comes from.</t>
         </is>
       </c>
     </row>
@@ -4926,88 +5072,98 @@
           <t>Nullable</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Base entity</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>Column comment</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>Alias (business name)</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="G4" s="56" t="inlineStr">
+      <c r="H4" s="56" t="inlineStr">
+        <is>
+          <t>Role (structural)</t>
+        </is>
+      </c>
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Is primary key</t>
         </is>
       </c>
-      <c r="H4" s="56" t="inlineStr">
+      <c r="J4" s="56" t="inlineStr">
         <is>
           <t>PII (column)</t>
         </is>
       </c>
-      <c r="I4" s="56" t="inlineStr">
+      <c r="K4" s="56" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
-      <c r="J4" s="56" t="inlineStr">
+      <c r="L4" s="56" t="inlineStr">
         <is>
           <t>FK references</t>
         </is>
       </c>
-      <c r="K4" s="56" t="inlineStr">
+      <c r="M4" s="56" t="inlineStr">
         <is>
           <t>Date format</t>
         </is>
       </c>
-      <c r="L4" s="56" t="inlineStr">
+      <c r="N4" s="56" t="inlineStr">
         <is>
           <t>Timezone</t>
         </is>
       </c>
-      <c r="M4" s="56" t="inlineStr">
+      <c r="O4" s="56" t="inlineStr">
         <is>
           <t>Measure — aggregation</t>
         </is>
       </c>
-      <c r="N4" s="56" t="inlineStr">
+      <c r="P4" s="56" t="inlineStr">
         <is>
           <t>Measure — safe dims</t>
         </is>
       </c>
-      <c r="O4" s="56" t="inlineStr">
+      <c r="Q4" s="56" t="inlineStr">
         <is>
           <t>Measure — warning</t>
         </is>
       </c>
-      <c r="P4" s="56" t="inlineStr">
+      <c r="R4" s="56" t="inlineStr">
         <is>
           <t>Measure — unit</t>
         </is>
       </c>
-      <c r="Q4" s="56" t="inlineStr">
+      <c r="S4" s="56" t="inlineStr">
         <is>
           <t>Measure — methodology</t>
         </is>
       </c>
-      <c r="R4" s="56" t="inlineStr">
+      <c r="T4" s="56" t="inlineStr">
         <is>
           <t>Glossary term link</t>
         </is>
       </c>
-      <c r="S4" s="56" t="inlineStr">
+      <c r="U4" s="56" t="inlineStr">
         <is>
           <t>Internal notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="56" customHeight="1">
       <c r="A5" s="57" t="inlineStr">
         <is>
           <t>Exact column name as in the table.</t>
@@ -5025,80 +5181,90 @@
       </c>
       <c r="D5" s="57" t="inlineStr">
         <is>
+          <t>The conformed entity this column comes from. Blank for fact-local columns.</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>How this column relates to its base entity. Free text — see conventions.</t>
+        </is>
+      </c>
+      <c r="F5" s="57" t="inlineStr">
+        <is>
           <t>Public business meaning. One sentence. Becomes column COMMENT in UC.</t>
         </is>
       </c>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="G5" s="57" t="inlineStr">
         <is>
           <t>Human-readable name consumers see in reports.</t>
         </is>
       </c>
-      <c r="F5" s="57" t="inlineStr">
-        <is>
-          <t>What this column does in the table. Dropdown.</t>
-        </is>
-      </c>
-      <c r="G5" s="57" t="inlineStr">
+      <c r="H5" s="57" t="inlineStr">
+        <is>
+          <t>Structural role in the table. Dropdown.</t>
+        </is>
+      </c>
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>yes if this column is part of the table's primary key. Dropdown.</t>
         </is>
       </c>
-      <c r="H5" s="57" t="inlineStr">
+      <c r="J5" s="57" t="inlineStr">
         <is>
           <t>yes if this specific column contains PII. Dropdown.</t>
         </is>
       </c>
-      <c r="I5" s="57" t="inlineStr">
+      <c r="K5" s="57" t="inlineStr">
         <is>
           <t>For enumerations: comma-separated list. Becomes a CHECK constraint.</t>
         </is>
       </c>
-      <c r="J5" s="57" t="inlineStr">
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>If foreign key, the target column. Format: schema.table.column</t>
         </is>
       </c>
-      <c r="K5" s="57" t="inlineStr">
+      <c r="M5" s="57" t="inlineStr">
         <is>
           <t>For DATE/TIMESTAMP only. The display format. Dropdown.</t>
         </is>
       </c>
-      <c r="L5" s="57" t="inlineStr">
-        <is>
-          <t>For TIMESTAMP only. The timezone the timestamp represents. Dropdown.</t>
-        </is>
-      </c>
-      <c r="M5" s="57" t="inlineStr">
+      <c r="N5" s="57" t="inlineStr">
+        <is>
+          <t>For TIMESTAMP only. Dropdown.</t>
+        </is>
+      </c>
+      <c r="O5" s="57" t="inlineStr">
         <is>
           <t>For measures only. How the measure behaves under aggregation. Dropdown.</t>
         </is>
       </c>
-      <c r="N5" s="57" t="inlineStr">
-        <is>
-          <t>For semi-additive measures: dimensions over which sum is valid. Comma-separated.</t>
-        </is>
-      </c>
-      <c r="O5" s="57" t="inlineStr">
+      <c r="P5" s="57" t="inlineStr">
+        <is>
+          <t>For semi-additive measures: dimensions over which sum is valid.</t>
+        </is>
+      </c>
+      <c r="Q5" s="57" t="inlineStr">
         <is>
           <t>For non-additive measures: warning to display to consumers.</t>
         </is>
       </c>
-      <c r="P5" s="57" t="inlineStr">
-        <is>
-          <t>For measures only. Unit of the value. Dropdown.</t>
-        </is>
-      </c>
-      <c r="Q5" s="57" t="inlineStr">
-        <is>
-          <t>For measures only. Engine and version that produced this measure. Dropdown or free text.</t>
-        </is>
-      </c>
       <c r="R5" s="57" t="inlineStr">
         <is>
+          <t>For measures only. Dropdown.</t>
+        </is>
+      </c>
+      <c r="S5" s="57" t="inlineStr">
+        <is>
+          <t>For measures only. Engine and version that produced this measure.</t>
+        </is>
+      </c>
+      <c r="T5" s="57" t="inlineStr">
+        <is>
           <t>Optional URL or term-ID linking to the Risk Data Catalog entry.</t>
         </is>
       </c>
-      <c r="S5" s="57" t="inlineStr">
+      <c r="U5" s="57" t="inlineStr">
         <is>
           <t>Not published. For the data team's reference.</t>
         </is>
@@ -5120,46 +5286,51 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>surrogate key</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Synthetic unique identifier for each issuer exposure row.</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>Issuer Exposure Key</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr"/>
-      <c r="I6" s="24" t="inlineStr"/>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr"/>
-      <c r="M6" s="24" t="inlineStr"/>
-      <c r="N6" s="24" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr"/>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="24" t="inlineStr"/>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="M6" s="24" t="n"/>
+      <c r="N6" s="24" t="n"/>
+      <c r="O6" s="24" t="n"/>
+      <c r="P6" s="24" t="n"/>
+      <c r="Q6" s="24" t="n"/>
+      <c r="R6" s="24" t="n"/>
+      <c r="S6" s="24" t="n"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>agreement</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr"/>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
@@ -5179,44 +5350,53 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
+          <t>Agreement</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>foreign key</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
           <t>Identifier of the collateral agreement under which exposure arose.</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>Agreement ID</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr"/>
-      <c r="I7" s="24" t="inlineStr"/>
-      <c r="J7" s="24" t="inlineStr">
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="24" t="n"/>
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr"/>
-      <c r="M7" s="24" t="inlineStr"/>
-      <c r="N7" s="24" t="inlineStr"/>
-      <c r="O7" s="24" t="inlineStr"/>
-      <c r="P7" s="24" t="inlineStr"/>
-      <c r="Q7" s="24" t="inlineStr"/>
-      <c r="R7" s="24" t="inlineStr">
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="n"/>
+      <c r="O7" s="24" t="n"/>
+      <c r="P7" s="24" t="n"/>
+      <c r="Q7" s="24" t="n"/>
+      <c r="R7" s="24" t="n"/>
+      <c r="S7" s="24" t="n"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>agreement</t>
         </is>
       </c>
-      <c r="S7" s="24" t="inlineStr"/>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
@@ -5236,115 +5416,132 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>trading counterparty</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
           <t>Counterparty facing TD under this exposure.</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>Counterparty Code</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr"/>
-      <c r="I8" s="24" t="inlineStr"/>
-      <c r="J8" s="24" t="inlineStr">
+      <c r="J8" s="24" t="n"/>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="inlineStr">
         <is>
           <t>d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr"/>
-      <c r="M8" s="24" t="inlineStr"/>
-      <c r="N8" s="24" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr"/>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="24" t="inlineStr"/>
-      <c r="R8" s="24" t="inlineStr">
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="24" t="n"/>
+      <c r="P8" s="24" t="n"/>
+      <c r="Q8" s="24" t="n"/>
+      <c r="R8" s="24" t="n"/>
+      <c r="S8" s="24" t="n"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>counterparty</t>
         </is>
       </c>
-      <c r="S8" s="24" t="inlineStr"/>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>as_of_date</t>
+          <t>guarantor_counterparty_code</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>guarantor</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Counterparty providing guarantee for the exposure, if any.</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Guarantor</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>Calculation snapshot date.</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>As Of Date</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>dimension</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr"/>
-      <c r="I9" s="24" t="inlineStr"/>
-      <c r="J9" s="24" t="inlineStr"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="L9" s="24" t="inlineStr"/>
-      <c r="M9" s="24" t="inlineStr"/>
-      <c r="N9" s="24" t="inlineStr"/>
-      <c r="O9" s="24" t="inlineStr"/>
-      <c r="P9" s="24" t="inlineStr"/>
-      <c r="Q9" s="24" t="inlineStr"/>
-      <c r="R9" s="24" t="inlineStr">
-        <is>
-          <t>as_of_date</t>
-        </is>
-      </c>
-      <c r="S9" s="24" t="inlineStr"/>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>creditrisk.xvala_xva.star_dim_counterparty.counterparty_code</t>
+        </is>
+      </c>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="24" t="n"/>
+      <c r="O9" s="24" t="n"/>
+      <c r="P9" s="24" t="n"/>
+      <c r="Q9" s="24" t="n"/>
+      <c r="R9" s="24" t="n"/>
+      <c r="S9" s="24" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>issuer_name</t>
+          <t>as_of_date</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>STRING</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -5354,49 +5551,58 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>Name of the issuer of the collateral instrument.</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>Issuer Name</t>
+          <t>foreign key</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
+          <t>Calculation snapshot date.</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>As Of Date</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H10" s="24" t="inlineStr"/>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>Sovereign, Bank, Corporate, Supranational, Agency</t>
-        </is>
-      </c>
-      <c r="J10" s="24" t="inlineStr"/>
-      <c r="K10" s="24" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr"/>
-      <c r="M10" s="24" t="inlineStr"/>
-      <c r="N10" s="24" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr"/>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="24" t="inlineStr"/>
-      <c r="R10" s="24" t="inlineStr">
-        <is>
-          <t>issuer</t>
-        </is>
-      </c>
-      <c r="S10" s="24" t="inlineStr"/>
+      <c r="J10" s="24" t="n"/>
+      <c r="K10" s="24" t="n"/>
+      <c r="L10" s="24" t="n"/>
+      <c r="M10" s="24" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="24" t="n"/>
+      <c r="P10" s="24" t="n"/>
+      <c r="Q10" s="24" t="n"/>
+      <c r="R10" s="24" t="n"/>
+      <c r="S10" s="24" t="n"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>as_of_date</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>issuer_type</t>
+          <t>issuer_name</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
@@ -5411,49 +5617,58 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>Type of issuer.</t>
+          <t>Issuer</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Issuer Type</t>
+          <t>denormalised attribute (name)</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
+          <t>Name of the issuer of the collateral instrument.</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Issuer Name</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr"/>
       <c r="I11" s="24" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
           <t>Sovereign, Bank, Corporate, Supranational, Agency</t>
         </is>
       </c>
-      <c r="J11" s="24" t="inlineStr"/>
-      <c r="K11" s="24" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr"/>
-      <c r="M11" s="24" t="inlineStr"/>
-      <c r="N11" s="24" t="inlineStr"/>
-      <c r="O11" s="24" t="inlineStr"/>
-      <c r="P11" s="24" t="inlineStr"/>
-      <c r="Q11" s="24" t="inlineStr"/>
-      <c r="R11" s="24" t="inlineStr">
-        <is>
-          <t>issuer_type</t>
-        </is>
-      </c>
-      <c r="S11" s="24" t="inlineStr"/>
+      <c r="L11" s="24" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="24" t="n"/>
+      <c r="O11" s="24" t="n"/>
+      <c r="P11" s="24" t="n"/>
+      <c r="Q11" s="24" t="n"/>
+      <c r="R11" s="24" t="n"/>
+      <c r="S11" s="24" t="n"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>issuer</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>issuer_rating</t>
+          <t>issuer_type</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
@@ -5463,147 +5678,149 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>External credit rating of the issuer at as_of_date.</t>
+          <t>Issuer</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>Issuer Rating</t>
+          <t>denormalised attribute (type)</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
+          <t>Type of issuer.</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Issuer Type</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr"/>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>AAA, AA+, AA, AA-, A+, A, A-, BBB+, BBB, BBB-, BB+, BB, BB-, NR</t>
-        </is>
-      </c>
-      <c r="J12" s="24" t="inlineStr"/>
-      <c r="K12" s="24" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr"/>
-      <c r="M12" s="24" t="inlineStr">
-        <is>
-          <t>semi-additive</t>
-        </is>
-      </c>
-      <c r="N12" s="24" t="inlineStr">
-        <is>
-          <t>counterparty, agreement, issuer</t>
-        </is>
-      </c>
-      <c r="O12" s="24" t="inlineStr">
-        <is>
-          <t>Do not sum across as_of_date — use latest snapshot value.</t>
-        </is>
-      </c>
-      <c r="P12" s="24" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="Q12" s="24" t="inlineStr">
-        <is>
-          <t>CCR_ENGINE_v4.2</t>
-        </is>
-      </c>
-      <c r="R12" s="24" t="inlineStr">
-        <is>
-          <t>credit_rating</t>
-        </is>
-      </c>
-      <c r="S12" s="24" t="inlineStr"/>
+      <c r="J12" s="24" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>Sovereign, Bank, Corporate, Supranational, Agency</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="n"/>
+      <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="24" t="n"/>
+      <c r="P12" s="24" t="n"/>
+      <c r="Q12" s="24" t="n"/>
+      <c r="R12" s="24" t="n"/>
+      <c r="S12" s="24" t="n"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>issuer_type</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>collateral_value</t>
+          <t>issuer_rating</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2)</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>denormalised attribute (rating)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>External credit rating of the issuer at as_of_date.</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Issuer Rating</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>Market value of collateral posted, USD-equivalent at as_of_date FX.</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>Collateral Value</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>measure</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr"/>
-      <c r="I13" s="24" t="inlineStr"/>
-      <c r="J13" s="24" t="inlineStr"/>
-      <c r="K13" s="24" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr"/>
-      <c r="M13" s="24" t="inlineStr">
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>AAA, AA+, AA, AA-, A+, A, A-, BBB+, BBB, BBB-, BB+, BB, BB-, NR</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="n"/>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>semi-additive</t>
         </is>
       </c>
-      <c r="N13" s="24" t="inlineStr">
+      <c r="P13" s="24" t="inlineStr">
         <is>
           <t>counterparty, agreement, issuer</t>
         </is>
       </c>
-      <c r="O13" s="24" t="inlineStr">
+      <c r="Q13" s="24" t="inlineStr">
         <is>
           <t>Do not sum across as_of_date — use latest snapshot value.</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr">
+      <c r="R13" s="24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="Q13" s="24" t="inlineStr">
+      <c r="S13" s="24" t="inlineStr">
         <is>
           <t>CCR_ENGINE_v4.2</t>
         </is>
       </c>
-      <c r="R13" s="24" t="inlineStr">
-        <is>
-          <t>collateral_value</t>
-        </is>
-      </c>
-      <c r="S13" s="24" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>credit_rating</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>indirect_exposure</t>
+          <t>collateral_value</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
@@ -5616,80 +5833,77 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>Indirect exposure to the issuer arising from the collateral, USD-equivalent.</t>
-        </is>
-      </c>
+      <c r="D14" s="24" t="inlineStr"/>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Indirect Exposure</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
+          <t>Market value of collateral posted, USD-equivalent at as_of_date FX.</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Collateral Value</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr"/>
-      <c r="I14" s="24" t="inlineStr"/>
-      <c r="J14" s="24" t="inlineStr"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD HH:MM:SS</t>
-        </is>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>UTC</t>
-        </is>
-      </c>
-      <c r="M14" s="24" t="inlineStr">
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="24" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="24" t="n"/>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>semi-additive</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr">
         <is>
           <t>counterparty, agreement, issuer</t>
         </is>
       </c>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="Q14" s="24" t="inlineStr">
         <is>
           <t>Do not sum across as_of_date — use latest snapshot value.</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr">
+      <c r="R14" s="24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="Q14" s="24" t="inlineStr">
+      <c r="S14" s="24" t="inlineStr">
         <is>
           <t>CCR_ENGINE_v4.2</t>
         </is>
       </c>
-      <c r="R14" s="24" t="inlineStr">
-        <is>
-          <t>indirect_exposure</t>
-        </is>
-      </c>
-      <c r="S14" s="24" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>collateral_value</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="8" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>load_timestamp</t>
+          <t>indirect_exposure</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DECIMAL(18,2)</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -5697,480 +5911,553 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>When this row was loaded.</t>
-        </is>
-      </c>
+      <c r="D15" s="25" t="inlineStr"/>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>Load Timestamp</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>Indirect exposure to the issuer arising from the collateral, USD-equivalent.</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
+          <t>Indirect Exposure</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr"/>
-      <c r="I15" s="25" t="inlineStr"/>
-      <c r="J15" s="25" t="inlineStr"/>
-      <c r="K15" s="25" t="inlineStr">
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="25" t="inlineStr">
         <is>
           <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
+      <c r="N15" s="25" t="inlineStr">
         <is>
           <t>UTC</t>
         </is>
       </c>
-      <c r="M15" s="25" t="inlineStr"/>
-      <c r="N15" s="25" t="inlineStr"/>
-      <c r="O15" s="25" t="inlineStr"/>
-      <c r="P15" s="25" t="inlineStr"/>
-      <c r="Q15" s="25" t="inlineStr"/>
-      <c r="R15" s="25" t="inlineStr"/>
-      <c r="S15" s="25" t="inlineStr"/>
+      <c r="O15" s="25" t="inlineStr">
+        <is>
+          <t>semi-additive</t>
+        </is>
+      </c>
+      <c r="P15" s="25" t="inlineStr">
+        <is>
+          <t>counterparty, agreement, issuer</t>
+        </is>
+      </c>
+      <c r="Q15" s="25" t="inlineStr">
+        <is>
+          <t>Do not sum across as_of_date — use latest snapshot value.</t>
+        </is>
+      </c>
+      <c r="R15" s="25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="S15" s="25" t="inlineStr">
+        <is>
+          <t>CCR_ENGINE_v4.2</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>indirect_exposure</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
+          <t>load_timestamp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>When this row was loaded.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Load Timestamp</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
           <t>Add additional columns below:</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="24" t="inlineStr"/>
-      <c r="B17" s="24" t="inlineStr"/>
-      <c r="C17" s="24" t="inlineStr"/>
-      <c r="D17" s="24" t="inlineStr"/>
-      <c r="E17" s="24" t="inlineStr"/>
-      <c r="F17" s="24" t="inlineStr"/>
-      <c r="G17" s="24" t="inlineStr"/>
-      <c r="H17" s="24" t="inlineStr"/>
-      <c r="I17" s="24" t="inlineStr"/>
-      <c r="J17" s="24" t="inlineStr"/>
-      <c r="K17" s="24" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr"/>
-      <c r="M17" s="24" t="inlineStr"/>
-      <c r="N17" s="24" t="inlineStr"/>
-      <c r="O17" s="24" t="inlineStr"/>
-      <c r="P17" s="24" t="inlineStr"/>
-      <c r="Q17" s="24" t="inlineStr"/>
-      <c r="R17" s="24" t="inlineStr"/>
-      <c r="S17" s="24" t="inlineStr"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="24" t="n"/>
+      <c r="P17" s="24" t="n"/>
+      <c r="Q17" s="24" t="n"/>
+      <c r="R17" s="24" t="n"/>
+      <c r="S17" s="24" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="24" t="inlineStr"/>
-      <c r="B18" s="24" t="inlineStr"/>
-      <c r="C18" s="24" t="inlineStr"/>
-      <c r="D18" s="24" t="inlineStr"/>
-      <c r="E18" s="24" t="inlineStr"/>
-      <c r="F18" s="24" t="inlineStr"/>
-      <c r="G18" s="24" t="inlineStr"/>
-      <c r="H18" s="24" t="inlineStr"/>
-      <c r="I18" s="24" t="inlineStr"/>
-      <c r="J18" s="24" t="inlineStr"/>
-      <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr"/>
-      <c r="M18" s="24" t="inlineStr"/>
-      <c r="N18" s="24" t="inlineStr"/>
-      <c r="O18" s="24" t="inlineStr"/>
-      <c r="P18" s="24" t="inlineStr"/>
-      <c r="Q18" s="24" t="inlineStr"/>
-      <c r="R18" s="24" t="inlineStr"/>
-      <c r="S18" s="24" t="inlineStr"/>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
+      <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="24" t="n"/>
+      <c r="P18" s="24" t="n"/>
+      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="24" t="n"/>
+      <c r="S18" s="24" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="24" t="inlineStr"/>
-      <c r="B19" s="24" t="inlineStr"/>
-      <c r="C19" s="24" t="inlineStr"/>
-      <c r="D19" s="24" t="inlineStr"/>
-      <c r="E19" s="24" t="inlineStr"/>
-      <c r="F19" s="24" t="inlineStr"/>
-      <c r="G19" s="24" t="inlineStr"/>
-      <c r="H19" s="24" t="inlineStr"/>
-      <c r="I19" s="24" t="inlineStr"/>
-      <c r="J19" s="24" t="inlineStr"/>
-      <c r="K19" s="24" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr"/>
-      <c r="M19" s="24" t="inlineStr"/>
-      <c r="N19" s="24" t="inlineStr"/>
-      <c r="O19" s="24" t="inlineStr"/>
-      <c r="P19" s="24" t="inlineStr"/>
-      <c r="Q19" s="24" t="inlineStr"/>
-      <c r="R19" s="24" t="inlineStr"/>
-      <c r="S19" s="24" t="inlineStr"/>
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="n"/>
+      <c r="O19" s="24" t="n"/>
+      <c r="P19" s="24" t="n"/>
+      <c r="Q19" s="24" t="n"/>
+      <c r="R19" s="24" t="n"/>
+      <c r="S19" s="24" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="24" t="inlineStr"/>
-      <c r="B20" s="24" t="inlineStr"/>
-      <c r="C20" s="24" t="inlineStr"/>
-      <c r="D20" s="24" t="inlineStr"/>
-      <c r="E20" s="24" t="inlineStr"/>
-      <c r="F20" s="24" t="inlineStr"/>
-      <c r="G20" s="24" t="inlineStr"/>
-      <c r="H20" s="24" t="inlineStr"/>
-      <c r="I20" s="24" t="inlineStr"/>
-      <c r="J20" s="24" t="inlineStr"/>
-      <c r="K20" s="24" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr"/>
-      <c r="M20" s="24" t="inlineStr"/>
-      <c r="N20" s="24" t="inlineStr"/>
-      <c r="O20" s="24" t="inlineStr"/>
-      <c r="P20" s="24" t="inlineStr"/>
-      <c r="Q20" s="24" t="inlineStr"/>
-      <c r="R20" s="24" t="inlineStr"/>
-      <c r="S20" s="24" t="inlineStr"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="24" t="n"/>
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="n"/>
+      <c r="L20" s="24" t="n"/>
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="24" t="n"/>
+      <c r="O20" s="24" t="n"/>
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="24" t="n"/>
+      <c r="R20" s="24" t="n"/>
+      <c r="S20" s="24" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="24" t="inlineStr"/>
-      <c r="B21" s="24" t="inlineStr"/>
-      <c r="C21" s="24" t="inlineStr"/>
-      <c r="D21" s="24" t="inlineStr"/>
-      <c r="E21" s="24" t="inlineStr"/>
-      <c r="F21" s="24" t="inlineStr"/>
-      <c r="G21" s="24" t="inlineStr"/>
-      <c r="H21" s="24" t="inlineStr"/>
-      <c r="I21" s="24" t="inlineStr"/>
-      <c r="J21" s="24" t="inlineStr"/>
-      <c r="K21" s="24" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr"/>
-      <c r="M21" s="24" t="inlineStr"/>
-      <c r="N21" s="24" t="inlineStr"/>
-      <c r="O21" s="24" t="inlineStr"/>
-      <c r="P21" s="24" t="inlineStr"/>
-      <c r="Q21" s="24" t="inlineStr"/>
-      <c r="R21" s="24" t="inlineStr"/>
-      <c r="S21" s="24" t="inlineStr"/>
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="24" t="n"/>
+      <c r="M21" s="24" t="n"/>
+      <c r="N21" s="24" t="n"/>
+      <c r="O21" s="24" t="n"/>
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="24" t="n"/>
+      <c r="S21" s="24" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="24" t="inlineStr"/>
-      <c r="B22" s="24" t="inlineStr"/>
-      <c r="C22" s="24" t="inlineStr"/>
-      <c r="D22" s="24" t="inlineStr"/>
-      <c r="E22" s="24" t="inlineStr"/>
-      <c r="F22" s="24" t="inlineStr"/>
-      <c r="G22" s="24" t="inlineStr"/>
-      <c r="H22" s="24" t="inlineStr"/>
-      <c r="I22" s="24" t="inlineStr"/>
-      <c r="J22" s="24" t="inlineStr"/>
-      <c r="K22" s="24" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr"/>
-      <c r="M22" s="24" t="inlineStr"/>
-      <c r="N22" s="24" t="inlineStr"/>
-      <c r="O22" s="24" t="inlineStr"/>
-      <c r="P22" s="24" t="inlineStr"/>
-      <c r="Q22" s="24" t="inlineStr"/>
-      <c r="R22" s="24" t="inlineStr"/>
-      <c r="S22" s="24" t="inlineStr"/>
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="24" t="n"/>
+      <c r="M22" s="24" t="n"/>
+      <c r="N22" s="24" t="n"/>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="24" t="n"/>
+      <c r="S22" s="24" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="24" t="inlineStr"/>
-      <c r="B23" s="24" t="inlineStr"/>
-      <c r="C23" s="24" t="inlineStr"/>
-      <c r="D23" s="24" t="inlineStr"/>
-      <c r="E23" s="24" t="inlineStr"/>
-      <c r="F23" s="24" t="inlineStr"/>
-      <c r="G23" s="24" t="inlineStr"/>
-      <c r="H23" s="24" t="inlineStr"/>
-      <c r="I23" s="24" t="inlineStr"/>
-      <c r="J23" s="24" t="inlineStr"/>
-      <c r="K23" s="24" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr"/>
-      <c r="M23" s="24" t="inlineStr"/>
-      <c r="N23" s="24" t="inlineStr"/>
-      <c r="O23" s="24" t="inlineStr"/>
-      <c r="P23" s="24" t="inlineStr"/>
-      <c r="Q23" s="24" t="inlineStr"/>
-      <c r="R23" s="24" t="inlineStr"/>
-      <c r="S23" s="24" t="inlineStr"/>
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="24" t="n"/>
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="n"/>
+      <c r="O23" s="24" t="n"/>
+      <c r="P23" s="24" t="n"/>
+      <c r="Q23" s="24" t="n"/>
+      <c r="R23" s="24" t="n"/>
+      <c r="S23" s="24" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="24" t="inlineStr"/>
-      <c r="B24" s="24" t="inlineStr"/>
-      <c r="C24" s="24" t="inlineStr"/>
-      <c r="D24" s="24" t="inlineStr"/>
-      <c r="E24" s="24" t="inlineStr"/>
-      <c r="F24" s="24" t="inlineStr"/>
-      <c r="G24" s="24" t="inlineStr"/>
-      <c r="H24" s="24" t="inlineStr"/>
-      <c r="I24" s="24" t="inlineStr"/>
-      <c r="J24" s="24" t="inlineStr"/>
-      <c r="K24" s="24" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr"/>
-      <c r="M24" s="24" t="inlineStr"/>
-      <c r="N24" s="24" t="inlineStr"/>
-      <c r="O24" s="24" t="inlineStr"/>
-      <c r="P24" s="24" t="inlineStr"/>
-      <c r="Q24" s="24" t="inlineStr"/>
-      <c r="R24" s="24" t="inlineStr"/>
-      <c r="S24" s="24" t="inlineStr"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="n"/>
+      <c r="O24" s="24" t="n"/>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="24" t="n"/>
+      <c r="S24" s="24" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="24" t="inlineStr"/>
-      <c r="B25" s="24" t="inlineStr"/>
-      <c r="C25" s="24" t="inlineStr"/>
-      <c r="D25" s="24" t="inlineStr"/>
-      <c r="E25" s="24" t="inlineStr"/>
-      <c r="F25" s="24" t="inlineStr"/>
-      <c r="G25" s="24" t="inlineStr"/>
-      <c r="H25" s="24" t="inlineStr"/>
-      <c r="I25" s="24" t="inlineStr"/>
-      <c r="J25" s="24" t="inlineStr"/>
-      <c r="K25" s="24" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr"/>
-      <c r="M25" s="24" t="inlineStr"/>
-      <c r="N25" s="24" t="inlineStr"/>
-      <c r="O25" s="24" t="inlineStr"/>
-      <c r="P25" s="24" t="inlineStr"/>
-      <c r="Q25" s="24" t="inlineStr"/>
-      <c r="R25" s="24" t="inlineStr"/>
-      <c r="S25" s="24" t="inlineStr"/>
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="n"/>
+      <c r="K25" s="24" t="n"/>
+      <c r="L25" s="24" t="n"/>
+      <c r="M25" s="24" t="n"/>
+      <c r="N25" s="24" t="n"/>
+      <c r="O25" s="24" t="n"/>
+      <c r="P25" s="24" t="n"/>
+      <c r="Q25" s="24" t="n"/>
+      <c r="R25" s="24" t="n"/>
+      <c r="S25" s="24" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="24" t="inlineStr"/>
-      <c r="B26" s="24" t="inlineStr"/>
-      <c r="C26" s="24" t="inlineStr"/>
-      <c r="D26" s="24" t="inlineStr"/>
-      <c r="E26" s="24" t="inlineStr"/>
-      <c r="F26" s="24" t="inlineStr"/>
-      <c r="G26" s="24" t="inlineStr"/>
-      <c r="H26" s="24" t="inlineStr"/>
-      <c r="I26" s="24" t="inlineStr"/>
-      <c r="J26" s="24" t="inlineStr"/>
-      <c r="K26" s="24" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr"/>
-      <c r="M26" s="24" t="inlineStr"/>
-      <c r="N26" s="24" t="inlineStr"/>
-      <c r="O26" s="24" t="inlineStr"/>
-      <c r="P26" s="24" t="inlineStr"/>
-      <c r="Q26" s="24" t="inlineStr"/>
-      <c r="R26" s="24" t="inlineStr"/>
-      <c r="S26" s="24" t="inlineStr"/>
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="24" t="n"/>
+      <c r="M26" s="24" t="n"/>
+      <c r="N26" s="24" t="n"/>
+      <c r="O26" s="24" t="n"/>
+      <c r="P26" s="24" t="n"/>
+      <c r="Q26" s="24" t="n"/>
+      <c r="R26" s="24" t="n"/>
+      <c r="S26" s="24" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="24" t="inlineStr"/>
-      <c r="B27" s="24" t="inlineStr"/>
-      <c r="C27" s="24" t="inlineStr"/>
-      <c r="D27" s="24" t="inlineStr"/>
-      <c r="E27" s="24" t="inlineStr"/>
-      <c r="F27" s="24" t="inlineStr"/>
-      <c r="G27" s="24" t="inlineStr"/>
-      <c r="H27" s="24" t="inlineStr"/>
-      <c r="I27" s="24" t="inlineStr"/>
-      <c r="J27" s="24" t="inlineStr"/>
-      <c r="K27" s="24" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr"/>
-      <c r="M27" s="24" t="inlineStr"/>
-      <c r="N27" s="24" t="inlineStr"/>
-      <c r="O27" s="24" t="inlineStr"/>
-      <c r="P27" s="24" t="inlineStr"/>
-      <c r="Q27" s="24" t="inlineStr"/>
-      <c r="R27" s="24" t="inlineStr"/>
-      <c r="S27" s="24" t="inlineStr"/>
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="24" t="n"/>
+      <c r="M27" s="24" t="n"/>
+      <c r="N27" s="24" t="n"/>
+      <c r="O27" s="24" t="n"/>
+      <c r="P27" s="24" t="n"/>
+      <c r="Q27" s="24" t="n"/>
+      <c r="R27" s="24" t="n"/>
+      <c r="S27" s="24" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="24" t="inlineStr"/>
-      <c r="B28" s="24" t="inlineStr"/>
-      <c r="C28" s="24" t="inlineStr"/>
-      <c r="D28" s="24" t="inlineStr"/>
-      <c r="E28" s="24" t="inlineStr"/>
-      <c r="F28" s="24" t="inlineStr"/>
-      <c r="G28" s="24" t="inlineStr"/>
-      <c r="H28" s="24" t="inlineStr"/>
-      <c r="I28" s="24" t="inlineStr"/>
-      <c r="J28" s="24" t="inlineStr"/>
-      <c r="K28" s="24" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr"/>
-      <c r="M28" s="24" t="inlineStr"/>
-      <c r="N28" s="24" t="inlineStr"/>
-      <c r="O28" s="24" t="inlineStr"/>
-      <c r="P28" s="24" t="inlineStr"/>
-      <c r="Q28" s="24" t="inlineStr"/>
-      <c r="R28" s="24" t="inlineStr"/>
-      <c r="S28" s="24" t="inlineStr"/>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="24" t="n"/>
+      <c r="M28" s="24" t="n"/>
+      <c r="N28" s="24" t="n"/>
+      <c r="O28" s="24" t="n"/>
+      <c r="P28" s="24" t="n"/>
+      <c r="Q28" s="24" t="n"/>
+      <c r="R28" s="24" t="n"/>
+      <c r="S28" s="24" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="24" t="inlineStr"/>
-      <c r="B29" s="24" t="inlineStr"/>
-      <c r="C29" s="24" t="inlineStr"/>
-      <c r="D29" s="24" t="inlineStr"/>
-      <c r="E29" s="24" t="inlineStr"/>
-      <c r="F29" s="24" t="inlineStr"/>
-      <c r="G29" s="24" t="inlineStr"/>
-      <c r="H29" s="24" t="inlineStr"/>
-      <c r="I29" s="24" t="inlineStr"/>
-      <c r="J29" s="24" t="inlineStr"/>
-      <c r="K29" s="24" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr"/>
-      <c r="M29" s="24" t="inlineStr"/>
-      <c r="N29" s="24" t="inlineStr"/>
-      <c r="O29" s="24" t="inlineStr"/>
-      <c r="P29" s="24" t="inlineStr"/>
-      <c r="Q29" s="24" t="inlineStr"/>
-      <c r="R29" s="24" t="inlineStr"/>
-      <c r="S29" s="24" t="inlineStr"/>
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="24" t="n"/>
+      <c r="M29" s="24" t="n"/>
+      <c r="N29" s="24" t="n"/>
+      <c r="O29" s="24" t="n"/>
+      <c r="P29" s="24" t="n"/>
+      <c r="Q29" s="24" t="n"/>
+      <c r="R29" s="24" t="n"/>
+      <c r="S29" s="24" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="24" t="inlineStr"/>
-      <c r="B30" s="24" t="inlineStr"/>
-      <c r="C30" s="24" t="inlineStr"/>
-      <c r="D30" s="24" t="inlineStr"/>
-      <c r="E30" s="24" t="inlineStr"/>
-      <c r="F30" s="24" t="inlineStr"/>
-      <c r="G30" s="24" t="inlineStr"/>
-      <c r="H30" s="24" t="inlineStr"/>
-      <c r="I30" s="24" t="inlineStr"/>
-      <c r="J30" s="24" t="inlineStr"/>
-      <c r="K30" s="24" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr"/>
-      <c r="M30" s="24" t="inlineStr"/>
-      <c r="N30" s="24" t="inlineStr"/>
-      <c r="O30" s="24" t="inlineStr"/>
-      <c r="P30" s="24" t="inlineStr"/>
-      <c r="Q30" s="24" t="inlineStr"/>
-      <c r="R30" s="24" t="inlineStr"/>
-      <c r="S30" s="24" t="inlineStr"/>
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="24" t="n"/>
+      <c r="M30" s="24" t="n"/>
+      <c r="N30" s="24" t="n"/>
+      <c r="O30" s="24" t="n"/>
+      <c r="P30" s="24" t="n"/>
+      <c r="Q30" s="24" t="n"/>
+      <c r="R30" s="24" t="n"/>
+      <c r="S30" s="24" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="24" t="inlineStr"/>
-      <c r="B31" s="24" t="inlineStr"/>
-      <c r="C31" s="24" t="inlineStr"/>
-      <c r="D31" s="24" t="inlineStr"/>
-      <c r="E31" s="24" t="inlineStr"/>
-      <c r="F31" s="24" t="inlineStr"/>
-      <c r="G31" s="24" t="inlineStr"/>
-      <c r="H31" s="24" t="inlineStr"/>
-      <c r="I31" s="24" t="inlineStr"/>
-      <c r="J31" s="24" t="inlineStr"/>
-      <c r="K31" s="24" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr"/>
-      <c r="M31" s="24" t="inlineStr"/>
-      <c r="N31" s="24" t="inlineStr"/>
-      <c r="O31" s="24" t="inlineStr"/>
-      <c r="P31" s="24" t="inlineStr"/>
-      <c r="Q31" s="24" t="inlineStr"/>
-      <c r="R31" s="24" t="inlineStr"/>
-      <c r="S31" s="24" t="inlineStr"/>
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="n"/>
+      <c r="K31" s="24" t="n"/>
+      <c r="L31" s="24" t="n"/>
+      <c r="M31" s="24" t="n"/>
+      <c r="N31" s="24" t="n"/>
+      <c r="O31" s="24" t="n"/>
+      <c r="P31" s="24" t="n"/>
+      <c r="Q31" s="24" t="n"/>
+      <c r="R31" s="24" t="n"/>
+      <c r="S31" s="24" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="24" t="inlineStr"/>
-      <c r="B32" s="24" t="inlineStr"/>
-      <c r="C32" s="24" t="inlineStr"/>
-      <c r="D32" s="24" t="inlineStr"/>
-      <c r="E32" s="24" t="inlineStr"/>
-      <c r="F32" s="24" t="inlineStr"/>
-      <c r="G32" s="24" t="inlineStr"/>
-      <c r="H32" s="24" t="inlineStr"/>
-      <c r="I32" s="24" t="inlineStr"/>
-      <c r="J32" s="24" t="inlineStr"/>
-      <c r="K32" s="24" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr"/>
-      <c r="M32" s="24" t="inlineStr"/>
-      <c r="N32" s="24" t="inlineStr"/>
-      <c r="O32" s="24" t="inlineStr"/>
-      <c r="P32" s="24" t="inlineStr"/>
-      <c r="Q32" s="24" t="inlineStr"/>
-      <c r="R32" s="24" t="inlineStr"/>
-      <c r="S32" s="24" t="inlineStr"/>
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="24" t="n"/>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="24" t="n"/>
+      <c r="M32" s="24" t="n"/>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="24" t="n"/>
+      <c r="P32" s="24" t="n"/>
+      <c r="Q32" s="24" t="n"/>
+      <c r="R32" s="24" t="n"/>
+      <c r="S32" s="24" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="24" t="inlineStr"/>
-      <c r="B33" s="24" t="inlineStr"/>
-      <c r="C33" s="24" t="inlineStr"/>
-      <c r="D33" s="24" t="inlineStr"/>
-      <c r="E33" s="24" t="inlineStr"/>
-      <c r="F33" s="24" t="inlineStr"/>
-      <c r="G33" s="24" t="inlineStr"/>
-      <c r="H33" s="24" t="inlineStr"/>
-      <c r="I33" s="24" t="inlineStr"/>
-      <c r="J33" s="24" t="inlineStr"/>
-      <c r="K33" s="24" t="inlineStr"/>
-      <c r="L33" s="24" t="inlineStr"/>
-      <c r="M33" s="24" t="inlineStr"/>
-      <c r="N33" s="24" t="inlineStr"/>
-      <c r="O33" s="24" t="inlineStr"/>
-      <c r="P33" s="24" t="inlineStr"/>
-      <c r="Q33" s="24" t="inlineStr"/>
-      <c r="R33" s="24" t="inlineStr"/>
-      <c r="S33" s="24" t="inlineStr"/>
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="n"/>
+      <c r="K33" s="24" t="n"/>
+      <c r="L33" s="24" t="n"/>
+      <c r="M33" s="24" t="n"/>
+      <c r="N33" s="24" t="n"/>
+      <c r="O33" s="24" t="n"/>
+      <c r="P33" s="24" t="n"/>
+      <c r="Q33" s="24" t="n"/>
+      <c r="R33" s="24" t="n"/>
+      <c r="S33" s="24" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="24" t="inlineStr"/>
-      <c r="B34" s="24" t="inlineStr"/>
-      <c r="C34" s="24" t="inlineStr"/>
-      <c r="D34" s="24" t="inlineStr"/>
-      <c r="E34" s="24" t="inlineStr"/>
-      <c r="F34" s="24" t="inlineStr"/>
-      <c r="G34" s="24" t="inlineStr"/>
-      <c r="H34" s="24" t="inlineStr"/>
-      <c r="I34" s="24" t="inlineStr"/>
-      <c r="J34" s="24" t="inlineStr"/>
-      <c r="K34" s="24" t="inlineStr"/>
-      <c r="L34" s="24" t="inlineStr"/>
-      <c r="M34" s="24" t="inlineStr"/>
-      <c r="N34" s="24" t="inlineStr"/>
-      <c r="O34" s="24" t="inlineStr"/>
-      <c r="P34" s="24" t="inlineStr"/>
-      <c r="Q34" s="24" t="inlineStr"/>
-      <c r="R34" s="24" t="inlineStr"/>
-      <c r="S34" s="24" t="inlineStr"/>
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="n"/>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="n"/>
+      <c r="O34" s="24" t="n"/>
+      <c r="P34" s="24" t="n"/>
+      <c r="Q34" s="24" t="n"/>
+      <c r="R34" s="24" t="n"/>
+      <c r="S34" s="24" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="24" t="inlineStr"/>
-      <c r="B35" s="24" t="inlineStr"/>
-      <c r="C35" s="24" t="inlineStr"/>
-      <c r="D35" s="24" t="inlineStr"/>
-      <c r="E35" s="24" t="inlineStr"/>
-      <c r="F35" s="24" t="inlineStr"/>
-      <c r="G35" s="24" t="inlineStr"/>
-      <c r="H35" s="24" t="inlineStr"/>
-      <c r="I35" s="24" t="inlineStr"/>
-      <c r="J35" s="24" t="inlineStr"/>
-      <c r="K35" s="24" t="inlineStr"/>
-      <c r="L35" s="24" t="inlineStr"/>
-      <c r="M35" s="24" t="inlineStr"/>
-      <c r="N35" s="24" t="inlineStr"/>
-      <c r="O35" s="24" t="inlineStr"/>
-      <c r="P35" s="24" t="inlineStr"/>
-      <c r="Q35" s="24" t="inlineStr"/>
-      <c r="R35" s="24" t="inlineStr"/>
-      <c r="S35" s="24" t="inlineStr"/>
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="24" t="n"/>
+      <c r="K35" s="24" t="n"/>
+      <c r="L35" s="24" t="n"/>
+      <c r="M35" s="24" t="n"/>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="24" t="n"/>
+      <c r="P35" s="24" t="n"/>
+      <c r="Q35" s="24" t="n"/>
+      <c r="R35" s="24" t="n"/>
+      <c r="S35" s="24" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="24" t="inlineStr"/>
-      <c r="B36" s="24" t="inlineStr"/>
-      <c r="C36" s="24" t="inlineStr"/>
-      <c r="D36" s="24" t="inlineStr"/>
-      <c r="E36" s="24" t="inlineStr"/>
-      <c r="F36" s="24" t="inlineStr"/>
-      <c r="G36" s="24" t="inlineStr"/>
-      <c r="H36" s="24" t="inlineStr"/>
-      <c r="I36" s="24" t="inlineStr"/>
-      <c r="J36" s="24" t="inlineStr"/>
-      <c r="K36" s="24" t="inlineStr"/>
-      <c r="L36" s="24" t="inlineStr"/>
-      <c r="M36" s="24" t="inlineStr"/>
-      <c r="N36" s="24" t="inlineStr"/>
-      <c r="O36" s="24" t="inlineStr"/>
-      <c r="P36" s="24" t="inlineStr"/>
-      <c r="Q36" s="24" t="inlineStr"/>
-      <c r="R36" s="24" t="inlineStr"/>
-      <c r="S36" s="24" t="inlineStr"/>
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
+      <c r="M36" s="24" t="n"/>
+      <c r="N36" s="24" t="n"/>
+      <c r="O36" s="24" t="n"/>
+      <c r="P36" s="24" t="n"/>
+      <c r="Q36" s="24" t="n"/>
+      <c r="R36" s="24" t="n"/>
+      <c r="S36" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A16:S16"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
-  </mergeCells>
   <dataValidations count="10">
     <dataValidation sqref="B6:B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STRING,INT,BIGINT,SMALLINT,TINYINT,FLOAT,DOUBLE,DECIMAL,DATE,TIMESTAMP,BOOLEAN,BINARY,ARRAY,MAP,STRUCT,VARIANT"</formula1>
@@ -6178,28 +6465,28 @@
     <dataValidation sqref="C6:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"key,measure,dimension,audit"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:G45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6:I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J6:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M6:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YYYY-MM-DD,YYYY-MM-DD HH:MM:SS"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N6:N45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EST,UTC,America/New_York"</formula1>
     </dataValidation>
-    <dataValidation sqref="M6:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"additive,semi-additive,non-additive"</formula1>
     </dataValidation>
-    <dataValidation sqref="P6:P45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R6:R45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"USD,EUR,percent,count,bps,ratio,days"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q6:Q45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S6:S45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CCR_ENGINE_v4.2,SA-CCR,CEM,internal_model,vendor_xva"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6215,13 +6502,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -6254,32 +6541,42 @@
           <t>Provider</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>Contract ID</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>Aligned entity</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Distribution method</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Refresh cadence</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Fallback feed</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Vendor flag</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Last reviewed</t>
         </is>
@@ -6296,32 +6593,42 @@
           <t>Murex</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>murex</t>
+        </is>
+      </c>
+      <c r="D5" s="83" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>File drop</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Daily by 06:00 EST</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>TAMS (manual)</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6338,32 +6645,42 @@
           <t>GoldenSource</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
+        <is>
+          <t>goldensource</t>
+        </is>
+      </c>
+      <c r="D6" s="83" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>Daily by 05:30 EST</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6380,32 +6697,42 @@
           <t>GLEIF</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
+        <is>
+          <t>gleif</t>
+        </is>
+      </c>
+      <c r="D7" s="83" t="inlineStr">
+        <is>
+          <t>Legal Entity</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>GoldenSource internal LEI</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6422,32 +6749,42 @@
           <t>MIDAS</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="83" t="inlineStr">
+        <is>
+          <t>midas</t>
+        </is>
+      </c>
+      <c r="D8" s="83" t="inlineStr">
+        <is>
+          <t>Currency (rate, not entity)</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>Daily by 06:00 EST</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>Bloomberg FX (manual)</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6464,32 +6801,42 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="83" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="D9" s="83" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>File drop</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
@@ -6506,32 +6853,32 @@
           <t>S&amp;P Global</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>File drop</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Moody's</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6548,32 +6895,32 @@
           <t>Moody's</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>File drop</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6590,32 +6937,32 @@
           <t>S&amp;P Global</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>File drop</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
@@ -6632,32 +6979,32 @@
           <t>XVALA internal</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Intraday</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Intraday</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -6666,12 +7013,12 @@
     <row r="14" ht="8" customHeight="1">
       <c r="A14" s="25" t="inlineStr"/>
       <c r="B14" s="25" t="inlineStr"/>
-      <c r="C14" s="25" t="inlineStr"/>
-      <c r="D14" s="25" t="inlineStr"/>
       <c r="E14" s="25" t="inlineStr"/>
       <c r="F14" s="25" t="inlineStr"/>
       <c r="G14" s="25" t="inlineStr"/>
       <c r="H14" s="25" t="inlineStr"/>
+      <c r="I14" s="25" t="inlineStr"/>
+      <c r="J14" s="25" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -6683,159 +7030,154 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="28" t="inlineStr"/>
       <c r="B16" s="28" t="inlineStr"/>
-      <c r="C16" s="28" t="inlineStr"/>
-      <c r="D16" s="28" t="inlineStr"/>
       <c r="E16" s="28" t="inlineStr"/>
       <c r="F16" s="28" t="inlineStr"/>
       <c r="G16" s="28" t="inlineStr"/>
       <c r="H16" s="28" t="inlineStr"/>
+      <c r="I16" s="28" t="inlineStr"/>
+      <c r="J16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="28" t="inlineStr"/>
       <c r="B17" s="28" t="inlineStr"/>
-      <c r="C17" s="28" t="inlineStr"/>
-      <c r="D17" s="28" t="inlineStr"/>
       <c r="E17" s="28" t="inlineStr"/>
       <c r="F17" s="28" t="inlineStr"/>
       <c r="G17" s="28" t="inlineStr"/>
       <c r="H17" s="28" t="inlineStr"/>
+      <c r="I17" s="28" t="inlineStr"/>
+      <c r="J17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="28" t="inlineStr"/>
       <c r="B18" s="28" t="inlineStr"/>
-      <c r="C18" s="28" t="inlineStr"/>
-      <c r="D18" s="28" t="inlineStr"/>
       <c r="E18" s="28" t="inlineStr"/>
       <c r="F18" s="28" t="inlineStr"/>
       <c r="G18" s="28" t="inlineStr"/>
       <c r="H18" s="28" t="inlineStr"/>
+      <c r="I18" s="28" t="inlineStr"/>
+      <c r="J18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="28" t="inlineStr"/>
       <c r="B19" s="28" t="inlineStr"/>
-      <c r="C19" s="28" t="inlineStr"/>
-      <c r="D19" s="28" t="inlineStr"/>
       <c r="E19" s="28" t="inlineStr"/>
       <c r="F19" s="28" t="inlineStr"/>
       <c r="G19" s="28" t="inlineStr"/>
       <c r="H19" s="28" t="inlineStr"/>
+      <c r="I19" s="28" t="inlineStr"/>
+      <c r="J19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="28" t="inlineStr"/>
       <c r="B20" s="28" t="inlineStr"/>
-      <c r="C20" s="28" t="inlineStr"/>
-      <c r="D20" s="28" t="inlineStr"/>
       <c r="E20" s="28" t="inlineStr"/>
       <c r="F20" s="28" t="inlineStr"/>
       <c r="G20" s="28" t="inlineStr"/>
       <c r="H20" s="28" t="inlineStr"/>
+      <c r="I20" s="28" t="inlineStr"/>
+      <c r="J20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="28" t="inlineStr"/>
       <c r="B21" s="28" t="inlineStr"/>
-      <c r="C21" s="28" t="inlineStr"/>
-      <c r="D21" s="28" t="inlineStr"/>
       <c r="E21" s="28" t="inlineStr"/>
       <c r="F21" s="28" t="inlineStr"/>
       <c r="G21" s="28" t="inlineStr"/>
       <c r="H21" s="28" t="inlineStr"/>
+      <c r="I21" s="28" t="inlineStr"/>
+      <c r="J21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="28" t="inlineStr"/>
       <c r="B22" s="28" t="inlineStr"/>
-      <c r="C22" s="28" t="inlineStr"/>
-      <c r="D22" s="28" t="inlineStr"/>
       <c r="E22" s="28" t="inlineStr"/>
       <c r="F22" s="28" t="inlineStr"/>
       <c r="G22" s="28" t="inlineStr"/>
       <c r="H22" s="28" t="inlineStr"/>
+      <c r="I22" s="28" t="inlineStr"/>
+      <c r="J22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="28" t="inlineStr"/>
       <c r="B23" s="28" t="inlineStr"/>
-      <c r="C23" s="28" t="inlineStr"/>
-      <c r="D23" s="28" t="inlineStr"/>
       <c r="E23" s="28" t="inlineStr"/>
       <c r="F23" s="28" t="inlineStr"/>
       <c r="G23" s="28" t="inlineStr"/>
       <c r="H23" s="28" t="inlineStr"/>
+      <c r="I23" s="28" t="inlineStr"/>
+      <c r="J23" s="28" t="inlineStr"/>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="28" t="inlineStr"/>
       <c r="B24" s="28" t="inlineStr"/>
-      <c r="C24" s="28" t="inlineStr"/>
-      <c r="D24" s="28" t="inlineStr"/>
       <c r="E24" s="28" t="inlineStr"/>
       <c r="F24" s="28" t="inlineStr"/>
       <c r="G24" s="28" t="inlineStr"/>
       <c r="H24" s="28" t="inlineStr"/>
+      <c r="I24" s="28" t="inlineStr"/>
+      <c r="J24" s="28" t="inlineStr"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="28" t="inlineStr"/>
       <c r="B25" s="28" t="inlineStr"/>
-      <c r="C25" s="28" t="inlineStr"/>
-      <c r="D25" s="28" t="inlineStr"/>
       <c r="E25" s="28" t="inlineStr"/>
       <c r="F25" s="28" t="inlineStr"/>
       <c r="G25" s="28" t="inlineStr"/>
       <c r="H25" s="28" t="inlineStr"/>
+      <c r="I25" s="28" t="inlineStr"/>
+      <c r="J25" s="28" t="inlineStr"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="28" t="inlineStr"/>
       <c r="B26" s="28" t="inlineStr"/>
-      <c r="C26" s="28" t="inlineStr"/>
-      <c r="D26" s="28" t="inlineStr"/>
       <c r="E26" s="28" t="inlineStr"/>
       <c r="F26" s="28" t="inlineStr"/>
       <c r="G26" s="28" t="inlineStr"/>
       <c r="H26" s="28" t="inlineStr"/>
+      <c r="I26" s="28" t="inlineStr"/>
+      <c r="J26" s="28" t="inlineStr"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="28" t="inlineStr"/>
       <c r="B27" s="28" t="inlineStr"/>
-      <c r="C27" s="28" t="inlineStr"/>
-      <c r="D27" s="28" t="inlineStr"/>
       <c r="E27" s="28" t="inlineStr"/>
       <c r="F27" s="28" t="inlineStr"/>
       <c r="G27" s="28" t="inlineStr"/>
       <c r="H27" s="28" t="inlineStr"/>
+      <c r="I27" s="28" t="inlineStr"/>
+      <c r="J27" s="28" t="inlineStr"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="28" t="inlineStr"/>
       <c r="B28" s="28" t="inlineStr"/>
-      <c r="C28" s="28" t="inlineStr"/>
-      <c r="D28" s="28" t="inlineStr"/>
       <c r="E28" s="28" t="inlineStr"/>
       <c r="F28" s="28" t="inlineStr"/>
       <c r="G28" s="28" t="inlineStr"/>
       <c r="H28" s="28" t="inlineStr"/>
+      <c r="I28" s="28" t="inlineStr"/>
+      <c r="J28" s="28" t="inlineStr"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="28" t="inlineStr"/>
       <c r="B29" s="28" t="inlineStr"/>
-      <c r="C29" s="28" t="inlineStr"/>
-      <c r="D29" s="28" t="inlineStr"/>
       <c r="E29" s="28" t="inlineStr"/>
       <c r="F29" s="28" t="inlineStr"/>
       <c r="G29" s="28" t="inlineStr"/>
       <c r="H29" s="28" t="inlineStr"/>
+      <c r="I29" s="28" t="inlineStr"/>
+      <c r="J29" s="28" t="inlineStr"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="28" t="inlineStr"/>
       <c r="B30" s="28" t="inlineStr"/>
-      <c r="C30" s="28" t="inlineStr"/>
-      <c r="D30" s="28" t="inlineStr"/>
       <c r="E30" s="28" t="inlineStr"/>
       <c r="F30" s="28" t="inlineStr"/>
       <c r="G30" s="28" t="inlineStr"/>
       <c r="H30" s="28" t="inlineStr"/>
+      <c r="I30" s="28" t="inlineStr"/>
+      <c r="J30" s="28" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="G5:G29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
@@ -6843,6 +7185,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6855,1710 +7198,1340 @@
   <dimension ref="A1:A246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="160" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sample YAML — ODCS v3 contract for star_fact_issuer_exposure</t>
+      <c r="A1" s="71" t="inlineStr">
+        <is>
+          <t>Sample YAML — ODCS v3 contract</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ODCS-compliant YAML. Each line on its own row for readability. Copy column A into a .yaml file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
+      <c r="A2" s="72" t="inlineStr">
+        <is>
+          <t>Generated from Columns + Table properties. Banner rows = section markers. Highlighted rows = section keys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1">
+      <c r="A3" s="65" t="n"/>
+    </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t># ODCS v3 Data Contract</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="73" t="inlineStr">
         <is>
           <t># Generated from Excel workbook for: d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A6" s="74" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>apiVersion: v3.0.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>kind: DataContract</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="74" t="inlineStr">
         <is>
           <t>id: star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>name: Daily snapshot of indirect issuer exposure from collateral postings</t>
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>name: "Daily snapshot of indirect issuer exposure from collateral postings"</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>version: 1.0.0</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t>status: active</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="74" t="inlineStr">
         <is>
           <t>domain: credit_risk</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A14" s="74" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t># Description block</t>
+      <c r="A15" s="75" t="inlineStr">
+        <is>
+          <t># ═══ DESCRIPTION — purpose, scope, business meaning ═══</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A16" s="69" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
-        <is>
-          <t># ═══ DESCRIPTION — purpose, scope, business meaning ═══</t>
+      <c r="A17" s="76" t="inlineStr">
+        <is>
+          <t>description:</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A18" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  purpose: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
-        <is>
-          <t>description:</t>
+      <c r="A19" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  includes: "Bilateral CSA agreements with eligible collateral. All counterparty regulatory regimes. End-of-day snapshots only."</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  purpose: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
+      <c r="A20" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  excludes: "Cleared trades. Exchange-traded positions. Tri-party agreements (handled by separate fact). Trades in WIP or terminated status."</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A21" s="74" t="inlineStr"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A22" s="77" t="inlineStr">
+        <is>
+          <t># ═══ TEAM — ownership and contacts ═══</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="59" t="inlineStr">
-        <is>
-          <t># ═══ TEAM — ownership and contacts ═══</t>
-        </is>
-      </c>
+      <c r="A23" s="78" t="inlineStr"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A24" s="79" t="inlineStr">
+        <is>
+          <t>team:</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
-        <is>
-          <t>team:</t>
+      <c r="A25" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - role: technicalOwner</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - role: technicalOwner</t>
+      <c r="A26" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    name: ccr_engine_team</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    name: ccr_engine_team</t>
-        </is>
-      </c>
+      <c r="A27" s="74" t="inlineStr"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A28" s="75" t="inlineStr">
+        <is>
+          <t># ═══ SLA — refresh cadence and timeliness commitments ═══</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A29" s="69" t="inlineStr"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="59" t="inlineStr">
-        <is>
-          <t># ═══ SLA — refresh cadence and timeliness commitments ═══</t>
+      <c r="A30" s="76" t="inlineStr">
+        <is>
+          <t>slaProperties:</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A31" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: frequency</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="60" t="inlineStr">
-        <is>
-          <t>slaProperties:</t>
+      <c r="A32" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: daily</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: frequency</t>
+      <c r="A33" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: refreshSLA</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: daily</t>
+      <c r="A34" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: "daily_by_07:00_EST"</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: refreshSLA</t>
-        </is>
-      </c>
+      <c r="A35" s="74" t="inlineStr"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: "daily_by_07:00_EST"</t>
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t># ═══ SCHEMA — columns with base entities, roles, types, constraints ═══</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A37" s="74" t="inlineStr"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A38" s="79" t="inlineStr">
+        <is>
+          <t>schema:</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="59" t="inlineStr">
-        <is>
-          <t># ═══ SCHEMA — columns, types, constraints, measure metadata ═══</t>
+      <c r="A39" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - name: star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A40" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    physicalName: d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="60" t="inlineStr">
-        <is>
-          <t>schema:</t>
+      <c r="A41" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    physicalType: fact</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - name: star_fact_issuer_exposure</t>
+      <c r="A42" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    description: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    physicalName: d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure</t>
-        </is>
-      </c>
+      <c r="A43" s="74" t="inlineStr"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    physicalType: fact</t>
+      <c r="A44" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    properties:</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    description: "Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer."</t>
+      <c r="A45" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: issuer_exposure_key</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="A46" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: BIGINT</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    properties:</t>
+      <c r="A47" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Synthetic unique identifier for each issuer exposure row."</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: issuer_exposure_key</t>
+      <c r="A48" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Issuer Exposure Key"</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: BIGINT</t>
+      <c r="A49" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "surrogate key"</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Synthetic unique identifier for each issuer exposure row."</t>
+      <c r="A50" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Issuer Exposure Key"</t>
+      <c r="A51" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id"</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="74" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: agreement_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: STRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Identifier of the collateral agreement under which exposure arose."</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Agreement ID"</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "foreign key"</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        primaryKey: true</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id"</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="74" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: counterparty_code</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: STRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Counterparty facing TD under this exposure."</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Counterparty Code"</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Counterparty</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "trading counterparty"</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        required: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        primaryKey: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code"</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="74" t="inlineStr"/>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: guarantor_counterparty_code</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: STRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Counterparty providing guarantee for the exposure, if any."</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Guarantor"</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Counterparty</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "guarantor"</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - "creditrisk.xvala_xva.star_dim_counterparty.counterparty_code"</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="74" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: as_of_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Calculation snapshot date."</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "As Of Date"</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "foreign key"</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        required: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        primaryKey: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="74" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: issuer_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: STRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Name of the issuer of the collateral instrument."</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Issuer Name"</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "denormalised attribute (name)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        required: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        primaryKey: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        allowedValues: [Sovereign, Bank, Corporate, Supranational, Agency]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="74" t="inlineStr"/>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: issuer_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: STRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Type of issuer."</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Issuer Type"</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "denormalised attribute (type)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        required: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        allowedValues: [Sovereign, Bank, Corporate, Supranational, Agency]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="74" t="inlineStr"/>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: issuer_rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: STRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "External credit rating of the issuer at as_of_date."</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Issuer Rating"</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        baseEntity: Issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "denormalised attribute (rating)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        allowedValues: [AAA, AA+, AA, AA-, A+, A, A-, BBB+, BBB, BBB-, BB+, BB, BB-, NR]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        unit: USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "key"</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: agreement_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Identifier of the collateral agreement under which exposure arose."</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Agreement ID"</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - property: x-measure-aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            value: semi-additive</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - property: x-measure-methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            value: CCR_ENGINE_v4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="74" t="inlineStr"/>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: collateral_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Market value of collateral posted, USD-equivalent at as_of_date FX."</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Collateral Value"</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "measure"</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        primaryKey: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id"</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        unit: USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "dimension"</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "agreement"</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: counterparty_code</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Counterparty facing TD under this exposure."</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Counterparty Code"</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - property: x-measure-aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            value: semi-additive</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - property: x-measure-methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            value: CCR_ENGINE_v4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="74" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: indirect_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "Indirect exposure to the issuer arising from the collateral, USD-equivalent."</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Indirect Exposure"</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "measure"</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        primaryKey: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code"</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="30" t="inlineStr">
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        unit: USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        customProperties:</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "dimension"</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "counterparty"</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: as_of_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Calculation snapshot date."</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "As Of Date"</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="30" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - property: x-measure-aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            value: semi-additive</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          - property: x-measure-methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            value: CCR_ENGINE_v4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="74" t="inlineStr"/>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - name: load_timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        logicalType: TIMESTAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        description: "When this row was loaded."</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        businessName: "Load Timestamp"</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        role: "audit"</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">        required: true</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        primaryKey: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "dimension"</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-date-format</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "YYYY-MM-DD"</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "as_of_date"</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: issuer_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Name of the issuer of the collateral instrument."</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Issuer Name"</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        required: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        primaryKey: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "dimension"</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "issuer"</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: issuer_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Type of issuer."</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Issuer Type"</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        required: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        validValues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "Sovereign"</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "Bank"</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "Corporate"</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "Supranational"</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "Agency"</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "dimension"</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "issuer_type"</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: issuer_rating</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: STRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "External credit rating of the issuer at as_of_date."</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Issuer Rating"</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        validValues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "AAA"</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "AA+"</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "AA"</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "AA-"</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "A+"</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "A"</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "A-"</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "BBB+"</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "BBB"</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "BBB-"</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "BB+"</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "BB"</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "BB-"</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - "NR"</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "dimension"</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "credit_rating"</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: collateral_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Market value of collateral posted, USD-equivalent at as_of_date FX."</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Collateral Value"</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        required: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="16" customHeight="1">
-      <c r="A159" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        unit: USD</t>
-        </is>
-      </c>
-    </row>
     <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
+      <c r="A160" s="74" t="inlineStr"/>
     </row>
     <row r="161" ht="16" customHeight="1">
-      <c r="A161" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
+      <c r="A161" s="75" t="inlineStr">
+        <is>
+          <t># ═══ CUSTOM PROPERTIES — TD-specific extensions (x-* tags) ═══</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "measure"</t>
-        </is>
-      </c>
+      <c r="A162" s="74" t="inlineStr"/>
     </row>
     <row r="163" ht="16" customHeight="1">
-      <c r="A163" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-aggregation</t>
+      <c r="A163" s="60" t="inlineStr">
+        <is>
+          <t>customProperties:</t>
         </is>
       </c>
     </row>
     <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "semi-additive"</t>
+      <c r="A164" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-source-app</t>
         </is>
       </c>
     </row>
     <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-safe-dims</t>
+      <c r="A165" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: xvala</t>
         </is>
       </c>
     </row>
     <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "counterparty, agreement, issuer"</t>
+      <c r="A166" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-classification</t>
         </is>
       </c>
     </row>
     <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-aggregation-warning</t>
+      <c r="A167" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: confidential</t>
         </is>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "Do not sum across as_of_date — use latest snapshot value."</t>
+      <c r="A168" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-scope-includes</t>
         </is>
       </c>
     </row>
     <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-methodology</t>
+      <c r="A169" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: "Bilateral CSA agreements with eligible collateral. All counterparty regulatory regimes. End-of-day snapshots only."</t>
         </is>
       </c>
     </row>
     <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "CCR_ENGINE_v4.2"</t>
+      <c r="A170" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - property: x-scope-excludes</t>
         </is>
       </c>
     </row>
     <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
+      <c r="A171" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    value: "Cleared trades. Exchange-traded positions. Tri-party agreements (handled by separate fact). Trades in WIP or terminated status."</t>
         </is>
       </c>
     </row>
     <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "collateral_value"</t>
-        </is>
-      </c>
+      <c r="A172" s="80" t="n"/>
     </row>
     <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A173" s="80" t="n"/>
     </row>
     <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: indirect_exposure</t>
-        </is>
-      </c>
+      <c r="A174" s="80" t="n"/>
     </row>
     <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: DECIMAL(18,2)</t>
-        </is>
-      </c>
+      <c r="A175" s="80" t="n"/>
     </row>
     <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "Indirect exposure to the issuer arising from the collateral, USD-equivalent."</t>
-        </is>
-      </c>
+      <c r="A176" s="80" t="n"/>
     </row>
     <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Indirect Exposure"</t>
-        </is>
-      </c>
+      <c r="A177" s="80" t="n"/>
     </row>
     <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        required: true</t>
-        </is>
-      </c>
+      <c r="A178" s="80" t="n"/>
     </row>
     <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        unit: USD</t>
-        </is>
-      </c>
+      <c r="A179" s="80" t="n"/>
     </row>
     <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
+      <c r="A180" s="80" t="n"/>
     </row>
     <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
+      <c r="A181" s="80" t="n"/>
     </row>
     <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "measure"</t>
-        </is>
-      </c>
+      <c r="A182" s="80" t="n"/>
     </row>
     <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-aggregation</t>
-        </is>
-      </c>
+      <c r="A183" s="80" t="n"/>
     </row>
     <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "semi-additive"</t>
-        </is>
-      </c>
+      <c r="A184" s="80" t="n"/>
     </row>
     <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-safe-dims</t>
-        </is>
-      </c>
+      <c r="A185" s="80" t="n"/>
     </row>
     <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "counterparty, agreement, issuer"</t>
-        </is>
-      </c>
+      <c r="A186" s="80" t="n"/>
     </row>
     <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-aggregation-warning</t>
-        </is>
-      </c>
+      <c r="A187" s="80" t="n"/>
     </row>
     <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "Do not sum across as_of_date — use latest snapshot value."</t>
-        </is>
-      </c>
+      <c r="A188" s="80" t="n"/>
     </row>
     <row r="189" ht="16" customHeight="1">
-      <c r="A189" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-methodology</t>
-        </is>
-      </c>
+      <c r="A189" s="80" t="n"/>
     </row>
     <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "CCR_ENGINE_v4.2"</t>
-        </is>
-      </c>
+      <c r="A190" s="80" t="n"/>
     </row>
     <row r="191" ht="16" customHeight="1">
-      <c r="A191" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-glossary-term</t>
-        </is>
-      </c>
+      <c r="A191" s="80" t="n"/>
     </row>
     <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "indirect_exposure"</t>
-        </is>
-      </c>
+      <c r="A192" s="80" t="n"/>
     </row>
     <row r="193" ht="16" customHeight="1">
-      <c r="A193" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A193" s="80" t="n"/>
     </row>
     <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - name: load_timestamp</t>
-        </is>
-      </c>
+      <c r="A194" s="80" t="n"/>
     </row>
     <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        logicalType: TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="A195" s="80" t="n"/>
     </row>
     <row r="196" ht="16" customHeight="1">
-      <c r="A196" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        description: "When this row was loaded."</t>
-        </is>
-      </c>
+      <c r="A196" s="80" t="n"/>
     </row>
     <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        businessName: "Load Timestamp"</t>
-        </is>
-      </c>
+      <c r="A197" s="80" t="n"/>
     </row>
     <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        required: true</t>
-        </is>
-      </c>
+      <c r="A198" s="80" t="n"/>
     </row>
     <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        customProperties:</t>
-        </is>
-      </c>
+      <c r="A199" s="80" t="n"/>
     </row>
     <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-column-role</t>
-        </is>
-      </c>
+      <c r="A200" s="80" t="n"/>
     </row>
     <row r="201" ht="16" customHeight="1">
-      <c r="A201" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "audit"</t>
-        </is>
-      </c>
+      <c r="A201" s="80" t="n"/>
     </row>
     <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-date-format</t>
-        </is>
-      </c>
+      <c r="A202" s="80" t="n"/>
     </row>
     <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "YYYY-MM-DD HH:MM:SS"</t>
-        </is>
-      </c>
+      <c r="A203" s="80" t="n"/>
     </row>
     <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          - property: x-timezone</t>
-        </is>
-      </c>
+      <c r="A204" s="80" t="n"/>
     </row>
     <row r="205" ht="16" customHeight="1">
-      <c r="A205" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            value: "UTC"</t>
-        </is>
-      </c>
+      <c r="A205" s="80" t="n"/>
     </row>
     <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A206" s="80" t="n"/>
     </row>
     <row r="207" ht="16" customHeight="1">
-      <c r="A207" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A207" s="80" t="n"/>
     </row>
     <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="29" t="inlineStr">
-        <is>
-          <t># TD-specific extensions (x-* customProperties)</t>
-        </is>
-      </c>
+      <c r="A208" s="80" t="n"/>
     </row>
     <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A209" s="65" t="n"/>
     </row>
     <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="59" t="inlineStr">
-        <is>
-          <t># ═══ CUSTOM PROPERTIES — TD-specific extensions (x-* tags) ═══</t>
-        </is>
-      </c>
+      <c r="A210" s="81" t="n"/>
     </row>
     <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A211" s="65" t="n"/>
     </row>
     <row r="212" ht="16" customHeight="1">
-      <c r="A212" s="60" t="inlineStr">
-        <is>
-          <t>customProperties:</t>
-        </is>
-      </c>
+      <c r="A212" s="80" t="n"/>
     </row>
     <row r="213" ht="16" customHeight="1">
-      <c r="A213" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-source-app</t>
-        </is>
-      </c>
+      <c r="A213" s="80" t="n"/>
     </row>
     <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: xvala</t>
-        </is>
-      </c>
+      <c r="A214" s="80" t="n"/>
     </row>
     <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-source-owner</t>
-        </is>
-      </c>
+      <c r="A215" s="80" t="n"/>
     </row>
     <row r="216" ht="16" customHeight="1">
-      <c r="A216" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: ccr_engine_team</t>
-        </is>
-      </c>
+      <c r="A216" s="80" t="n"/>
     </row>
     <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-load-pattern</t>
-        </is>
-      </c>
+      <c r="A217" s="80" t="n"/>
     </row>
     <row r="218" ht="16" customHeight="1">
-      <c r="A218" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: file_drop</t>
-        </is>
-      </c>
+      <c r="A218" s="80" t="n"/>
     </row>
     <row r="219" ht="16" customHeight="1">
-      <c r="A219" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: dataClassification</t>
-        </is>
-      </c>
+      <c r="A219" s="80" t="n"/>
     </row>
     <row r="220" ht="16" customHeight="1">
-      <c r="A220" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: confidential</t>
-        </is>
-      </c>
+      <c r="A220" s="80" t="n"/>
     </row>
     <row r="221" ht="16" customHeight="1">
-      <c r="A221" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-visible</t>
-        </is>
-      </c>
+      <c r="A221" s="80" t="n"/>
     </row>
     <row r="222" ht="16" customHeight="1">
-      <c r="A222" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: yes</t>
-        </is>
-      </c>
+      <c r="A222" s="80" t="n"/>
     </row>
     <row r="223" ht="16" customHeight="1">
-      <c r="A223" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- inherited from schema-level (set on ALTER SCHEMA) ----</t>
-        </is>
-      </c>
+      <c r="A223" s="80" t="n"/>
     </row>
     <row r="224" ht="16" customHeight="1">
-      <c r="A224" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-source-catalog-url</t>
-        </is>
-      </c>
+      <c r="A224" s="80" t="n"/>
     </row>
     <row r="225" ht="16" customHeight="1">
-      <c r="A225" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: "https://sharepoint.td.com/risk-data/xvala_source_catalog.xlsx"</t>
-        </is>
-      </c>
+      <c r="A225" s="80" t="n"/>
     </row>
     <row r="226" ht="16" customHeight="1">
-      <c r="A226" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-precedence-defaults</t>
-        </is>
-      </c>
+      <c r="A226" s="80" t="n"/>
     </row>
     <row r="227" ht="16" customHeight="1">
-      <c r="A227" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: "issuer_rating:sp&gt;moodys&gt;internal"</t>
-        </is>
-      </c>
+      <c r="A227" s="80" t="n"/>
     </row>
     <row r="228" ht="16" customHeight="1">
-      <c r="A228" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-currency-fx-source-default</t>
-        </is>
-      </c>
+      <c r="A228" s="80" t="n"/>
     </row>
     <row r="229" ht="16" customHeight="1">
-      <c r="A229" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: MIDAS</t>
-        </is>
-      </c>
+      <c r="A229" s="80" t="n"/>
     </row>
     <row r="230" ht="16" customHeight="1">
-      <c r="A230" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-source-calendar</t>
-        </is>
-      </c>
+      <c r="A230" s="80" t="n"/>
     </row>
     <row r="231" ht="16" customHeight="1">
-      <c r="A231" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: internal_business_calendar</t>
-        </is>
-      </c>
+      <c r="A231" s="80" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- currency handling (this table) ----</t>
-        </is>
-      </c>
+      <c r="A232" s="80" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-currency-applied</t>
-        </is>
-      </c>
+      <c r="A233" s="80" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: true</t>
-        </is>
-      </c>
+      <c r="A234" s="80" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-currency-reporting</t>
-        </is>
-      </c>
+      <c r="A235" s="80" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: USD</t>
-        </is>
-      </c>
+      <c r="A236" s="80" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-currency-fx-rate-date</t>
-        </is>
-      </c>
+      <c r="A237" s="80" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: business_date</t>
-        </is>
-      </c>
+      <c r="A238" s="80" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="61" t="n"/>
+      <c r="A239" s="80" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="61" t="n"/>
+      <c r="A240" s="80" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="61" t="n"/>
+      <c r="A241" s="80" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="61" t="n"/>
+      <c r="A242" s="80" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="61" t="n"/>
+      <c r="A243" s="80" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  # ---- internal notes (not consumer-facing) ----</t>
-        </is>
-      </c>
+      <c r="A244" s="80" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - property: x-internal-notes</t>
-        </is>
-      </c>
+      <c r="A245" s="80" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    value: "Late-arriving issuer ratings backfilled within 2 days of as_of_date."</t>
-        </is>
-      </c>
+      <c r="A246" s="80" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -8570,654 +8543,779 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="140" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sample DDL — Databricks SQL for star_fact_issuer_exposure</t>
+      <c r="A1" s="55" t="inlineStr">
+        <is>
+          <t>Sample DDL — star_fact_issuer_exposure</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Each row is one executable section. Copy column B statements into Databricks SQL editor — they run as-is.</t>
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>CREATE TABLE first (full structure + constraints). ALTER statements below for tags and post-creation modifications.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Statement (executable Databricks SQL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t>1. Schema tags</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>-- Schema-wide defaults. Apply once per schema.
-ALTER SCHEMA d4001_centralus_tdvip_creditrisk.xvala_xva
-  SET TAGS (
-    'x-app.source_catalog_url' = 'https://sharepoint.td.com/risk-data/xvala_source_catalog.xlsx',
-    'x-app.precedence' = 'issuer_rating:sp&gt;moodys&gt;internal',
-    'x-currency.fx_source' = 'MIDAS',
-    'x-source.calendar' = 'internal_business_calendar'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>2. Table comment</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>-- Plain-language description shown to consumers in the catalog.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  SET TBLPROPERTIES (
-    'comment' = 'Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer.'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="300" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>3. Table tags</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>-- Default-absent tags omitted (PII/issue/FX-applied/native-kept set only when true).
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  SET TAGS (
-    'source.app' = 'xvala',
-    'source.domain' = 'credit_risk',
-    'source.owner' = 'ccr_engine_team',
-    'source.pattern' = 'file_drop',
-    'owner.technical' = 'ccr_engine_team',
-    'class.sensitivity' = 'confidential',
-    'status' = 'active',
-    'visible' = 'yes',
-    'shape' = 'fact',
-    'refresh.frequency' = 'daily',
-    'refresh.sla' = 'daily_by_07:00_EST',
-    'x-currency.applied' = 'true',
-    'x-currency.reporting' = 'USD',
-    'x-currency.fx_rate_date' = 'business_date',
-    'x-issue' = 'true',
-    'x-issue.tracker' = 'JIRA-CCR-1847'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>4. Primary key</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>-- Composite PK across columns marked Is primary key=yes.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ADD CONSTRAINT pk_factissuerexposure
-    PRIMARY KEY (issuer_exposure_key, agreement_id, counterparty_code, as_of_date, issuer_name)
-    NOT ENFORCED;</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>5. Grain tag (derived)</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>-- Derived from PK columns; PK columns ARE the grain.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  SET TAGS (
-    'contract.grain' = 'issuer_exposure_key+agreement_id+counterparty_code+as_of_date+issuer_name'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>6. FK — agreement_id</t>
-        </is>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>-- agreement_id references d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement.agreement_id.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ADD CONSTRAINT fk_star_fact_is_agreementid
-    FOREIGN KEY (agreement_id)
-    REFERENCES d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_agreement(agreement_id)
-    NOT ENFORCED;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>6. FK — counterparty_code</t>
-        </is>
-      </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>-- counterparty_code references d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty.counterparty_code.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ADD CONSTRAINT fk_star_fact_is_counterpartycode
-    FOREIGN KEY (counterparty_code)
-    REFERENCES d4001_centralus_tdvip_creditrisk.xvala_xva.star_dim_counterparty(counterparty_code)
-    NOT ENFORCED;</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>7. CHECK — issuer_type</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>-- Enforced at write time. issuer_type must be one of the listed values.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ADD CONSTRAINT chk_star_fact_is_issuertype
-    CHECK (issuer_type IN ('Sovereign','Bank','Corporate','Supranational','Agency'));</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>7. CHECK — issuer_rating</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>-- Enforced at write time. issuer_rating must be one of the listed values.
-ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ADD CONSTRAINT chk_star_fact_is_issuerrating
-    CHECK (issuer_rating IN ('AAA','AA+','AA','AA-','A+','A','A-','BBB+','BBB','BBB-','BB+','BB','BB-','NR'));</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — issuer_exposure_key</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_exposure_key SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — agreement_id</t>
-        </is>
-      </c>
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN agreement_id SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — counterparty_code</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN counterparty_code SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — as_of_date</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN as_of_date SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — issuer_name</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_name SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — issuer_type</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_type SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — collateral_value</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN collateral_value SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — indirect_exposure</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN indirect_exposure SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>8. NOT NULL — load_timestamp</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN load_timestamp SET NOT NULL;</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — issuer_exposure_key</t>
-        </is>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_exposure_key COMMENT 'Synthetic unique identifier for each issuer exposure row.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — agreement_id</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN agreement_id COMMENT 'Identifier of the collateral agreement under which exposure arose.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — counterparty_code</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN counterparty_code COMMENT 'Counterparty facing TD under this exposure.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — as_of_date</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN as_of_date COMMENT 'Calculation snapshot date.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — issuer_name</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_name COMMENT 'Name of the issuer of the collateral instrument.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — issuer_type</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_type COMMENT 'Type of issuer.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — issuer_rating</t>
-        </is>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_rating COMMENT 'External credit rating of the issuer at as_of_date.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — collateral_value</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN collateral_value COMMENT 'Market value of collateral posted, USD-equivalent at as_of_date FX.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — indirect_exposure</t>
-        </is>
-      </c>
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN indirect_exposure COMMENT 'Indirect exposure to the issuer arising from the collateral, USD-equivalent.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>9. COMMENT — load_timestamp</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN load_timestamp COMMENT 'When this row was loaded.';</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="75" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — issuer_exposure_key</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_exposure_key SET TAGS (
-    'identity.alias' = 'Issuer Exposure Key',
-    'column.role' = 'key'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — agreement_id</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN agreement_id SET TAGS (
-    'identity.alias' = 'Agreement ID',
-    'column.role' = 'dimension',
-    'glossary.term' = 'agreement'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — counterparty_code</t>
-        </is>
-      </c>
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN counterparty_code SET TAGS (
-    'identity.alias' = 'Counterparty Code',
-    'column.role' = 'dimension',
-    'glossary.term' = 'counterparty'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="105" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — as_of_date</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN as_of_date SET TAGS (
-    'identity.alias' = 'As Of Date',
-    'column.role' = 'dimension',
-    'x-format.date_format' = 'YYYY-MM-DD',
-    'glossary.term' = 'as_of_date'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — issuer_name</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_name SET TAGS (
-    'identity.alias' = 'Issuer Name',
-    'column.role' = 'dimension',
-    'glossary.term' = 'issuer'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — issuer_type</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_type SET TAGS (
-    'identity.alias' = 'Issuer Type',
-    'column.role' = 'dimension',
-    'glossary.term' = 'issuer_type'
-  );</t>
-        </is>
-      </c>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>§ 1. CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="n"/>
+      <c r="C4" s="65" t="n"/>
+      <c r="D4" s="65" t="n"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="66" t="inlineStr"/>
+      <c r="B5" s="67" t="inlineStr">
+        <is>
+          <t>-- Full table creation with columns, types, NOT NULL, PK, FKs, CHECK, COMMENT</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="n"/>
+      <c r="D5" s="65" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="66" t="inlineStr"/>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>CREATE TABLE creditrisk.xvala_xva.star_fact_issuer_exposure (</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="n"/>
+      <c r="D6" s="65" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="66" t="inlineStr"/>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  issuer_exposure_key         BIGINT          NOT NULL COMMENT 'Synthetic unique identifier for each issuer exposure row',</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="n"/>
+      <c r="D7" s="65" t="n"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="66" t="inlineStr"/>
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  agreement_id                STRING          NOT NULL COMMENT 'Collateral agreement under which exposure arose',</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="n"/>
+      <c r="D8" s="65" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="66" t="inlineStr"/>
+      <c r="B9" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  counterparty_code           STRING          NOT NULL COMMENT 'Trading counterparty facing TD',</t>
+        </is>
+      </c>
+      <c r="C9" s="65" t="n"/>
+      <c r="D9" s="65" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="66" t="inlineStr"/>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  guarantor_counterparty_code STRING                   COMMENT 'Counterparty providing guarantee for the exposure, if any',</t>
+        </is>
+      </c>
+      <c r="C10" s="65" t="n"/>
+      <c r="D10" s="65" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="66" t="inlineStr"/>
+      <c r="B11" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as_of_date                  DATE            NOT NULL COMMENT 'Calculation snapshot date (business calendar)',</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="n"/>
+      <c r="D11" s="65" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="66" t="inlineStr"/>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  issuer_name                 STRING          NOT NULL COMMENT 'Name of collateral issuer (denormalised from Issuer)',</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="n"/>
+      <c r="D12" s="65" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="66" t="inlineStr"/>
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  issuer_type                 STRING          NOT NULL COMMENT 'Type of issuer (denormalised from Issuer)',</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="n"/>
+      <c r="D13" s="65" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="66" t="inlineStr"/>
+      <c r="B14" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  issuer_rating               STRING                   COMMENT 'External credit rating (denormalised from Issuer)',</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="n"/>
+      <c r="D14" s="65" t="n"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="66" t="inlineStr"/>
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  collateral_value            DECIMAL(18,2)   NOT NULL COMMENT 'Market value posted, USD',</t>
+        </is>
+      </c>
+      <c r="C15" s="65" t="n"/>
+      <c r="D15" s="65" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="66" t="inlineStr"/>
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  indirect_exposure           DECIMAL(18,2)   NOT NULL COMMENT 'USD exposure to issuer via collateral',</t>
+        </is>
+      </c>
+      <c r="C16" s="65" t="n"/>
+      <c r="D16" s="65" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="66" t="inlineStr"/>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  load_timestamp              TIMESTAMP       NOT NULL COMMENT 'When this row was loaded',</t>
+        </is>
+      </c>
+      <c r="C17" s="65" t="n"/>
+      <c r="D17" s="65" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="66" t="inlineStr"/>
+      <c r="B18" s="67" t="inlineStr"/>
+      <c r="C18" s="65" t="n"/>
+      <c r="D18" s="65" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="66" t="inlineStr"/>
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONSTRAINT pk_issuer_exposure</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="n"/>
+      <c r="D19" s="65" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="66" t="inlineStr"/>
+      <c r="B20" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PRIMARY KEY (agreement_id, counterparty_code, as_of_date, issuer_name) NOT ENFORCED,</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="n"/>
+      <c r="D20" s="65" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="66" t="inlineStr"/>
+      <c r="B21" s="67" t="inlineStr"/>
+      <c r="C21" s="65" t="n"/>
+      <c r="D21" s="65" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="66" t="inlineStr"/>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONSTRAINT fk_agreement</t>
+        </is>
+      </c>
+      <c r="C22" s="65" t="n"/>
+      <c r="D22" s="65" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="66" t="inlineStr"/>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (agreement_id)</t>
+        </is>
+      </c>
+      <c r="C23" s="65" t="n"/>
+      <c r="D23" s="65" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="66" t="inlineStr"/>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REFERENCES creditrisk.xvala_xva.star_dim_agreement(agreement_id) NOT ENFORCED,</t>
+        </is>
+      </c>
+      <c r="C24" s="65" t="n"/>
+      <c r="D24" s="65" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="66" t="inlineStr"/>
+      <c r="B25" s="67" t="inlineStr"/>
+      <c r="C25" s="65" t="n"/>
+      <c r="D25" s="65" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="66" t="inlineStr"/>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONSTRAINT fk_counterparty</t>
+        </is>
+      </c>
+      <c r="C26" s="65" t="n"/>
+      <c r="D26" s="65" t="n"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="66" t="inlineStr"/>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (counterparty_code)</t>
+        </is>
+      </c>
+      <c r="C27" s="65" t="n"/>
+      <c r="D27" s="65" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="66" t="inlineStr"/>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REFERENCES creditrisk.xvala_xva.star_dim_counterparty(counterparty_code) NOT ENFORCED,</t>
+        </is>
+      </c>
+      <c r="C28" s="65" t="n"/>
+      <c r="D28" s="65" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="66" t="inlineStr"/>
+      <c r="B29" s="67" t="inlineStr"/>
+      <c r="C29" s="65" t="n"/>
+      <c r="D29" s="65" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="66" t="inlineStr"/>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONSTRAINT fk_guarantor</t>
+        </is>
+      </c>
+      <c r="C30" s="65" t="n"/>
+      <c r="D30" s="65" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="66" t="inlineStr"/>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FOREIGN KEY (guarantor_counterparty_code)</t>
+        </is>
+      </c>
+      <c r="C31" s="65" t="n"/>
+      <c r="D31" s="65" t="n"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="66" t="inlineStr"/>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REFERENCES creditrisk.xvala_xva.star_dim_counterparty(counterparty_code) NOT ENFORCED,</t>
+        </is>
+      </c>
+      <c r="C32" s="65" t="n"/>
+      <c r="D32" s="65" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="66" t="inlineStr"/>
+      <c r="B33" s="67" t="inlineStr"/>
+      <c r="C33" s="65" t="n"/>
+      <c r="D33" s="65" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="66" t="inlineStr"/>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONSTRAINT chk_issuer_type</t>
+        </is>
+      </c>
+      <c r="C34" s="65" t="n"/>
+      <c r="D34" s="65" t="n"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="66" t="inlineStr"/>
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CHECK (issuer_type IN ('Sovereign','Bank','Corporate','Supranational','Agency'))</t>
+        </is>
+      </c>
+      <c r="C35" s="65" t="n"/>
+      <c r="D35" s="65" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="66" t="inlineStr"/>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>)</t>
+        </is>
+      </c>
+      <c r="C36" s="65" t="n"/>
+      <c r="D36" s="65" t="n"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="66" t="inlineStr"/>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>USING DELTA</t>
+        </is>
+      </c>
+      <c r="C37" s="65" t="n"/>
+      <c r="D37" s="65" t="n"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="66" t="inlineStr"/>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>COMMENT 'Daily snapshot of indirect issuer exposure from collateral postings. One row per agreement per counterparty per as-of date per issuer.';</t>
+        </is>
+      </c>
+      <c r="C38" s="65" t="n"/>
+      <c r="D38" s="65" t="n"/>
     </row>
     <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — issuer_rating</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN issuer_rating SET TAGS (
-    'identity.alias' = 'Issuer Rating',
-    'column.role' = 'dimension',
-    'glossary.term' = 'credit_rating'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="165" customHeight="1">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — collateral_value</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN collateral_value SET TAGS (
-    'identity.alias' = 'Collateral Value',
-    'column.role' = 'measure',
-    'x-measure.aggregation' = 'semi-additive',
-    'x-measure.safe_dims' = 'counterparty, agreement, issuer',
-    'x-measure.warning' = 'Do not sum across as_of_date — use latest snapshot value.',
-    'x-measure.unit' = 'USD',
-    'x-measure.methodology' = 'CCR_ENGINE_v4.2',
-    'glossary.term' = 'collateral_value'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="165" customHeight="1">
-      <c r="A41" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — indirect_exposure</t>
-        </is>
-      </c>
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN indirect_exposure SET TAGS (
-    'identity.alias' = 'Indirect Exposure',
-    'column.role' = 'measure',
-    'x-measure.aggregation' = 'semi-additive',
-    'x-measure.safe_dims' = 'counterparty, agreement, issuer',
-    'x-measure.warning' = 'Do not sum across as_of_date — use latest snapshot value.',
-    'x-measure.unit' = 'USD',
-    'x-measure.methodology' = 'CCR_ENGINE_v4.2',
-    'glossary.term' = 'indirect_exposure'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="105" customHeight="1">
-      <c r="A42" s="32" t="inlineStr">
-        <is>
-          <t>10. Column tags — load_timestamp</t>
-        </is>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>ALTER TABLE d4001_centralus_tdvip_creditrisk.xvala_xva.star_fact_issuer_exposure
-  ALTER COLUMN load_timestamp SET TAGS (
-    'identity.alias' = 'Load Timestamp',
-    'column.role' = 'audit',
-    'x-format.date_format' = 'YYYY-MM-DD HH:MM:SS',
-    'x-format.timezone' = 'UTC'
-  );</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="150" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>11. Verify</t>
-        </is>
-      </c>
-      <c r="B43" s="33" t="inlineStr">
-        <is>
-          <t>-- Verify the tags landed.
-SELECT * FROM system.information_schema.table_tags
-WHERE catalog_name = 'd4001_centralus_tdvip_creditrisk'
-  AND schema_name = 'xvala_xva'
-  AND table_name = 'star_fact_issuer_exposure';
-SELECT * FROM system.information_schema.column_tags
-WHERE catalog_name = 'd4001_centralus_tdvip_creditrisk'
-  AND schema_name = 'xvala_xva'
-  AND table_name = 'star_fact_issuer_exposure';</t>
+      <c r="A39" s="66" t="n"/>
+      <c r="B39" s="66" t="n"/>
+      <c r="C39" s="65" t="n"/>
+      <c r="D39" s="65" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="68" t="inlineStr">
+        <is>
+          <t>§ 2. SCHEMA-LEVEL TAGS</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="65" t="n"/>
+      <c r="D40" s="65" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="66" t="inlineStr"/>
+      <c r="B41" s="67" t="inlineStr">
+        <is>
+          <t>-- Tags inherited from schema; set once on the schema, not per table</t>
+        </is>
+      </c>
+      <c r="C41" s="65" t="n"/>
+      <c r="D41" s="65" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="66" t="inlineStr"/>
+      <c r="B42" s="67" t="inlineStr">
+        <is>
+          <t>ALTER SCHEMA creditrisk.xvala_xva</t>
+        </is>
+      </c>
+      <c r="C42" s="65" t="n"/>
+      <c r="D42" s="65" t="n"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="66" t="inlineStr"/>
+      <c r="B43" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SET TAGS ('x-contract-id' = 'XVALA_CCR_001');</t>
+        </is>
+      </c>
+      <c r="C43" s="65" t="n"/>
+      <c r="D43" s="65" t="n"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="B44" s="69" t="inlineStr">
+        <is>
+          <t>ALTER SCHEMA creditrisk.xvala_xva</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="B45" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SET TAGS ('x-currency-fx-source-default' = 'MIDAS');</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="70" t="inlineStr">
+        <is>
+          <t>§ 3. TABLE-LEVEL TAGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="B48" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="B49" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="B50" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'source.app' = 'xvala',</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="B51" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'refresh.frequency' = 'daily',</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="B52" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'refresh.sla' = 'daily_by_07:00_EST',</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="B53" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'class.sensitivity' = 'confidential',</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="B54" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'shape' = 'fact',</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="B55" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'x-scope-includes' = 'Bilateral CSA agreements with eligible collateral; all regimes',</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="B56" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'x-scope-excludes' = 'Cleared trades; exchange-traded positions; tri-party agreements'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="B57" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="70" t="inlineStr">
+        <is>
+          <t>§ 4. COLUMN-LEVEL TAGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="B60" s="69" t="inlineStr">
+        <is>
+          <t>-- Base entity + role declared as column tags for consumer + AI discoverability</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="B61" s="69" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="B62" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="B63" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN agreement_id SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="B64" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'base-entity' = 'Agreement', 'role' = 'foreign key'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="B65" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="B66" s="69" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="B67" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="B68" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN counterparty_code SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="B69" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'base-entity' = 'Counterparty', 'role' = 'trading counterparty'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="B70" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="B71" s="69" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="B72" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="B73" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN guarantor_counterparty_code SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="B74" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'base-entity' = 'Counterparty', 'role' = 'guarantor'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="B75" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="B76" s="69" t="inlineStr"/>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="B77" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="B78" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN issuer_name SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="B79" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'base-entity' = 'Issuer', 'role' = 'denormalised attribute (name)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="B80" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="B81" s="69" t="inlineStr"/>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="B82" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="B83" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN issuer_type SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="B84" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'base-entity' = 'Issuer', 'role' = 'denormalised attribute (type)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="B85" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="B86" s="69" t="inlineStr"/>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="B87" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="B88" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN issuer_rating SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="B89" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'base-entity' = 'Issuer', 'role' = 'denormalised attribute (rating)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="B90" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="B91" s="69" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="B92" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="B93" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN indirect_exposure SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="B94" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'unit' = 'USD',</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="B95" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'aggregation' = 'semi-additive',</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="B96" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'methodology' = 'CCR_ENGINE_v4.2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="B97" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="B98" s="69" t="inlineStr"/>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="B99" s="69" t="inlineStr">
+        <is>
+          <t>ALTER TABLE creditrisk.xvala_xva.star_fact_issuer_exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="B100" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALTER COLUMN collateral_value SET TAGS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="B101" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'unit' = 'USD', 'aggregation' = 'semi-additive'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="B102" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  );</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
